--- a/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="103">
   <si>
     <t>Marking type</t>
   </si>
@@ -24,6 +24,300 @@
     <t>Point number/name</t>
   </si>
   <si>
+    <t>Position X (m)</t>
+  </si>
+  <si>
+    <t>Position Y (m)</t>
+  </si>
+  <si>
+    <t>Position Z (m)</t>
+  </si>
+  <si>
+    <t>Wall Number</t>
+  </si>
+  <si>
+    <t>Shape type</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Quadrant</t>
+  </si>
+  <si>
+    <t>Unnamed : 9</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Orientation</t>
+  </si>
+  <si>
+    <t>Diameter</t>
+  </si>
+  <si>
+    <t>Tile</t>
+  </si>
+  <si>
+    <t>TMP1S2e4:TMP1S2e4:1155212</t>
+  </si>
+  <si>
+    <t>TMP1S2f1:TMP1S2f1:1155220</t>
+  </si>
+  <si>
+    <t>TMP1S2f2:TMP1S2f2:1155219</t>
+  </si>
+  <si>
+    <t>TMP1S2f3:TMP1S2f3:1155218</t>
+  </si>
+  <si>
+    <t>TMP1S2f4:TMP1S2f4:1155217</t>
+  </si>
+  <si>
+    <t>TMP1S2e1:TMP1S2e1:1155215</t>
+  </si>
+  <si>
+    <t>TMP1S2e2:TMP1S2e2:1155214</t>
+  </si>
+  <si>
+    <t>TMP1S2e3:TMP1S2e3:1155213</t>
+  </si>
+  <si>
+    <t>TMP1S2d1:TMP1S2d1:1155210</t>
+  </si>
+  <si>
+    <t>TMP1S2d2:TMP1S2d2:1155209</t>
+  </si>
+  <si>
+    <t>TMP1S2d3:TMP1S2d3:1155208</t>
+  </si>
+  <si>
+    <t>TMP1S2d4:TMP1S2d4:1155207</t>
+  </si>
+  <si>
+    <t>TMP1S2c1:TMP1S2c1:1155205</t>
+  </si>
+  <si>
+    <t>TMP1S2c2:TMP1S2c2:1155204</t>
+  </si>
+  <si>
+    <t>TMP1S2c4:TMP1S2c4:1155202</t>
+  </si>
+  <si>
+    <t>TMP1S2c3:TMP1S2c3:1155203</t>
+  </si>
+  <si>
+    <t>TMP1S2b2:TMP1S2b2:1155199</t>
+  </si>
+  <si>
+    <t>TMP1S2b3:TMP1S2b3:1155198</t>
+  </si>
+  <si>
+    <t>TMP1S2b4:TMP1S2b4:1155197</t>
+  </si>
+  <si>
+    <t>TMP1S2a1:TMP1S2a1:1155195</t>
+  </si>
+  <si>
+    <t>TMP1S2a2:TMP1S2a2:1155194</t>
+  </si>
+  <si>
+    <t>TMP1S2a3:TMP1S2a3:1155193</t>
+  </si>
+  <si>
+    <t>TMP1S2a4:TMP1S2a4:1155192</t>
+  </si>
+  <si>
+    <t>TMP1S2b1:TMP1S2b1:1155200</t>
+  </si>
+  <si>
+    <t>TMP2S2b2:TMP2S2b2:1155222</t>
+  </si>
+  <si>
+    <t>TMP2S2a2:TMP2S2a2:1155224</t>
+  </si>
+  <si>
+    <t>TMP2S2b1:TMP2S2b1:1155223</t>
+  </si>
+  <si>
+    <t>TMP2S2a1:TMP2S2a1:1155225</t>
+  </si>
+  <si>
+    <t>TMP3S2b3:TMP3S2b3:1155228</t>
+  </si>
+  <si>
+    <t>TMP3S2b1:TMP3S2b1:1155229</t>
+  </si>
+  <si>
+    <t>TMP3S2a4:TMP3S2a4:1155231</t>
+  </si>
+  <si>
+    <t>TMP3S2a3:TMP3S2a3:1155232</t>
+  </si>
+  <si>
+    <t>TMP3S2a2:TMP3S2a2:1155233</t>
+  </si>
+  <si>
+    <t>TMP3S2a1:TMP3S2a1:1155234</t>
+  </si>
+  <si>
+    <t>TMP3S2b4:TMP3S2b4:1155227</t>
+  </si>
+  <si>
+    <t>TMP3S2b2:TMP3S2b2:1155230</t>
+  </si>
+  <si>
+    <t>TMP4S2a4:TMP4S2a4:1155237</t>
+  </si>
+  <si>
+    <t>TMP4S2a1:TMP4S2a1:1155243</t>
+  </si>
+  <si>
+    <t>TMP4S2a2:TMP4S2a2:1155242</t>
+  </si>
+  <si>
+    <t>TMP4S2a3:TMP4S2a3:1155241</t>
+  </si>
+  <si>
+    <t>TMP5S2b3:TMP5S2b3:1155248</t>
+  </si>
+  <si>
+    <t>TMP5S2a2:TMP5S2a2:1155249</t>
+  </si>
+  <si>
+    <t>TMP5S2a3:TMP5S2a3:1155247</t>
+  </si>
+  <si>
+    <t>TMP5S2b2:TMP5S2b2:1155250</t>
+  </si>
+  <si>
+    <t>TMP5S2b1:TMP5S2b1:1155251</t>
+  </si>
+  <si>
+    <t>TMP5S2a1:TMP5S2a1:1155252</t>
+  </si>
+  <si>
+    <t>TMP5S2b4:TMP5S2b4:1155246</t>
+  </si>
+  <si>
+    <t>TMP5S2a4:TMP5S2a4:1155245</t>
+  </si>
+  <si>
+    <t>TMP4S2b2:TMP4S2b2:1155239</t>
+  </si>
+  <si>
+    <t>TMP4S2b3:TMP4S2b3:1155238</t>
+  </si>
+  <si>
+    <t>TMP4S2b4:TMP4S2b4:1155236</t>
+  </si>
+  <si>
+    <t>TMP4S2b1:TMP4S2b1:1155240</t>
+  </si>
+  <si>
+    <t>TMP6S2b1:TMP6S2b1:1155262</t>
+  </si>
+  <si>
+    <t>TMP6S2b2:TMP6S2b2:1155261</t>
+  </si>
+  <si>
+    <t>TMP6S2b4:TMP6S2b4:1155259</t>
+  </si>
+  <si>
+    <t>TMP6S2b3:TMP6S2b3:1155260</t>
+  </si>
+  <si>
+    <t>TMP6S2a2:TMP6S2a2:1155256</t>
+  </si>
+  <si>
+    <t>TMP6S2a4:TMP6S2a4:1155255</t>
+  </si>
+  <si>
+    <t>TMP6S2a3:TMP6S2a3:1155254</t>
+  </si>
+  <si>
+    <t>TMP6S2a1:TMP6S2a1:1155257</t>
+  </si>
+  <si>
+    <t>TMP7S2c2:TMP7S2c2:1155275</t>
+  </si>
+  <si>
+    <t>TMP7S2b3:TMP7S2b3:1155264</t>
+  </si>
+  <si>
+    <t>TMP7S2b2:TMP7S2b2:1155265</t>
+  </si>
+  <si>
+    <t>TMP7S2b1:TMP7S2b1:1155266</t>
+  </si>
+  <si>
+    <t>TMP7S2a3:TMP7S2a3:1155267</t>
+  </si>
+  <si>
+    <t>TMP7S2a2:TMP7S2a2:1155268</t>
+  </si>
+  <si>
+    <t>TMP7S2a1:TMP7S2a1:1155269</t>
+  </si>
+  <si>
+    <t>TMP7S2d1:TMP7S2d1:1155271</t>
+  </si>
+  <si>
+    <t>TMP7S2d2:TMP7S2d2:1155272</t>
+  </si>
+  <si>
+    <t>TMP7S2d3:TMP7S2d3:1155273</t>
+  </si>
+  <si>
+    <t>TMP7S2c3:TMP7S2c3:1155274</t>
+  </si>
+  <si>
+    <t>TMP7S2c1:TMP7S2c1:1155276</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>blank</t>
+  </si>
+  <si>
+    <t>Fitting</t>
+  </si>
+  <si>
+    <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
+  </si>
+  <si>
+    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+  </si>
+  <si>
+    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+  </si>
+  <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
+    <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>Position X (mm)</t>
   </si>
   <si>
@@ -31,297 +325,6 @@
   </si>
   <si>
     <t>Position Z (mm)</t>
-  </si>
-  <si>
-    <t>Wall Number</t>
-  </si>
-  <si>
-    <t>Shape type</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Quadrant</t>
-  </si>
-  <si>
-    <t>Unnamed : 9</t>
-  </si>
-  <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Orientation</t>
-  </si>
-  <si>
-    <t>Diameter</t>
-  </si>
-  <si>
-    <t>Tile</t>
-  </si>
-  <si>
-    <t>TMP1S2c3:TMP1S2c3:1155203</t>
-  </si>
-  <si>
-    <t>TMP1S2d1:TMP1S2d1:1155210</t>
-  </si>
-  <si>
-    <t>TMP1S2d2:TMP1S2d2:1155209</t>
-  </si>
-  <si>
-    <t>TMP1S2d3:TMP1S2d3:1155208</t>
-  </si>
-  <si>
-    <t>TMP1S2d4:TMP1S2d4:1155207</t>
-  </si>
-  <si>
-    <t>TMP1S2c1:TMP1S2c1:1155205</t>
-  </si>
-  <si>
-    <t>TMP1S2c2:TMP1S2c2:1155204</t>
-  </si>
-  <si>
-    <t>TMP1S2e2:TMP1S2e2:1155214</t>
-  </si>
-  <si>
-    <t>TMP1S2c4:TMP1S2c4:1155202</t>
-  </si>
-  <si>
-    <t>TMP1S2b1:TMP1S2b1:1155200</t>
-  </si>
-  <si>
-    <t>TMP1S2b2:TMP1S2b2:1155199</t>
-  </si>
-  <si>
-    <t>TMP1S2b3:TMP1S2b3:1155198</t>
-  </si>
-  <si>
-    <t>TMP1S2b4:TMP1S2b4:1155197</t>
-  </si>
-  <si>
-    <t>TMP1S2a1:TMP1S2a1:1155195</t>
-  </si>
-  <si>
-    <t>TMP1S2a2:TMP1S2a2:1155194</t>
-  </si>
-  <si>
-    <t>TMP1S2a3:TMP1S2a3:1155193</t>
-  </si>
-  <si>
-    <t>TMP1S2a4:TMP1S2a4:1155192</t>
-  </si>
-  <si>
-    <t>TMP1S2e1:TMP1S2e1:1155215</t>
-  </si>
-  <si>
-    <t>TMP1S2f4:TMP1S2f4:1155217</t>
-  </si>
-  <si>
-    <t>TMP1S2f3:TMP1S2f3:1155218</t>
-  </si>
-  <si>
-    <t>TMP1S2f2:TMP1S2f2:1155219</t>
-  </si>
-  <si>
-    <t>TMP1S2f1:TMP1S2f1:1155220</t>
-  </si>
-  <si>
-    <t>TMP1S2e4:TMP1S2e4:1155212</t>
-  </si>
-  <si>
-    <t>TMP1S2e3:TMP1S2e3:1155213</t>
-  </si>
-  <si>
-    <t>TMP2S2b2:TMP2S2b2:1155222</t>
-  </si>
-  <si>
-    <t>TMP2S2b1:TMP2S2b1:1155223</t>
-  </si>
-  <si>
-    <t>TMP2S2c1:TMP2S2c1:1156963</t>
-  </si>
-  <si>
-    <t>TMP2S2c2:TMP2S2c2:1156962</t>
-  </si>
-  <si>
-    <t>TMP2S2a2:TMP2S2a2:1155224</t>
-  </si>
-  <si>
-    <t>TMP2S2a1:TMP2S2a1:1155225</t>
-  </si>
-  <si>
-    <t>TMP3S2b3:TMP3S2b3:1155228</t>
-  </si>
-  <si>
-    <t>TMP3S2b1:TMP3S2b1:1155229</t>
-  </si>
-  <si>
-    <t>TMP3S2b2:TMP3S2b2:1155230</t>
-  </si>
-  <si>
-    <t>TMP3S2a3:TMP3S2a3:1155232</t>
-  </si>
-  <si>
-    <t>TMP3S2a2:TMP3S2a2:1155233</t>
-  </si>
-  <si>
-    <t>TMP3S2a1:TMP3S2a1:1155234</t>
-  </si>
-  <si>
-    <t>TMP3S2a4:TMP3S2a4:1155231</t>
-  </si>
-  <si>
-    <t>TMP3S2b4:TMP3S2b4:1155227</t>
-  </si>
-  <si>
-    <t>TMP4S2a4:TMP4S2a4:1155237</t>
-  </si>
-  <si>
-    <t>TMP4S2a1:TMP4S2a1:1155243</t>
-  </si>
-  <si>
-    <t>TMP4S2a3:TMP4S2a3:1155241</t>
-  </si>
-  <si>
-    <t>TMP4S2a2:TMP4S2a2:1155242</t>
-  </si>
-  <si>
-    <t>TMP5S2b1:TMP5S2b1:1155251</t>
-  </si>
-  <si>
-    <t>TMP5S2b2:TMP5S2b2:1155250</t>
-  </si>
-  <si>
-    <t>TMP5S2a2:TMP5S2a2:1155249</t>
-  </si>
-  <si>
-    <t>TMP5S2b3:TMP5S2b3:1155248</t>
-  </si>
-  <si>
-    <t>TMP5S2a3:TMP5S2a3:1155247</t>
-  </si>
-  <si>
-    <t>TMP5S2b4:TMP5S2b4:1155246</t>
-  </si>
-  <si>
-    <t>TMP5S2a4:TMP5S2a4:1155245</t>
-  </si>
-  <si>
-    <t>TMP5S2a1:TMP5S2a1:1155252</t>
-  </si>
-  <si>
-    <t>TMP4S2b2:TMP4S2b2:1155239</t>
-  </si>
-  <si>
-    <t>TMP4S2b1:TMP4S2b1:1155240</t>
-  </si>
-  <si>
-    <t>TMP4S2b4:TMP4S2b4:1155236</t>
-  </si>
-  <si>
-    <t>TMP4S2b3:TMP4S2b3:1155238</t>
-  </si>
-  <si>
-    <t>TMP6S2b1:TMP6S2b1:1155262</t>
-  </si>
-  <si>
-    <t>TMP6S2b3:TMP6S2b3:1155260</t>
-  </si>
-  <si>
-    <t>TMP6S2b2:TMP6S2b2:1155261</t>
-  </si>
-  <si>
-    <t>TMP6S2a1:TMP6S2a1:1155257</t>
-  </si>
-  <si>
-    <t>TMP6S2a2:TMP6S2a2:1155256</t>
-  </si>
-  <si>
-    <t>TMP6S2a4:TMP6S2a4:1155255</t>
-  </si>
-  <si>
-    <t>TMP6S2a3:TMP6S2a3:1155254</t>
-  </si>
-  <si>
-    <t>TMP6S2b4:TMP6S2b4:1155259</t>
-  </si>
-  <si>
-    <t>TMP7S2c1:TMP7S2c1:1155276</t>
-  </si>
-  <si>
-    <t>TMP7S2c2:TMP7S2c2:1155275</t>
-  </si>
-  <si>
-    <t>TMP7S2c3:TMP7S2c3:1155274</t>
-  </si>
-  <si>
-    <t>TMP7S2d3:TMP7S2d3:1155273</t>
-  </si>
-  <si>
-    <t>TMP7S2d2:TMP7S2d2:1155272</t>
-  </si>
-  <si>
-    <t>TMP7S2a1:TMP7S2a1:1155269</t>
-  </si>
-  <si>
-    <t>TMP7S2a2:TMP7S2a2:1155268</t>
-  </si>
-  <si>
-    <t>TMP7S2a3:TMP7S2a3:1155267</t>
-  </si>
-  <si>
-    <t>TMP7S2b1:TMP7S2b1:1155266</t>
-  </si>
-  <si>
-    <t>TMP7S2b3:TMP7S2b3:1155264</t>
-  </si>
-  <si>
-    <t>TMP7S2d1:TMP7S2d1:1155271</t>
-  </si>
-  <si>
-    <t>TMP7S2b2:TMP7S2b2:1155265</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>+</t>
-  </si>
-  <si>
-    <t>blank</t>
-  </si>
-  <si>
-    <t>Fitting</t>
-  </si>
-  <si>
-    <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
-  </si>
-  <si>
-    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
-  </si>
-  <si>
-    <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
-  </si>
-  <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
 </sst>
 </file>
@@ -679,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -728,7 +731,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -740,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-30</v>
+        <v>0.49</v>
       </c>
       <c r="F2">
-        <v>-175</v>
+        <v>1.025</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -752,21 +755,21 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -778,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>470</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F3">
-        <v>1025</v>
+        <v>1.025</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -790,21 +793,21 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -816,10 +819,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>470</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F4">
-        <v>425</v>
+        <v>0.425</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -828,21 +831,21 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M4">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -854,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>470</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F5">
-        <v>-175</v>
+        <v>-0.175</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -866,21 +869,21 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -892,10 +895,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>470</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F6">
-        <v>-775</v>
+        <v>-0.775</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -904,21 +907,21 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -930,10 +933,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>-30</v>
+        <v>0.49</v>
       </c>
       <c r="F7">
-        <v>1025</v>
+        <v>1.025</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -942,21 +945,21 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -968,10 +971,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-30</v>
+        <v>0.49</v>
       </c>
       <c r="F8">
-        <v>425</v>
+        <v>0.425</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -980,21 +983,21 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1006,10 +1009,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>490</v>
+        <v>0.49</v>
       </c>
       <c r="F9">
-        <v>425</v>
+        <v>-0.175</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1018,21 +1021,21 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1044,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>-30</v>
+        <v>0.47</v>
       </c>
       <c r="F10">
-        <v>-775</v>
+        <v>1.025</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1056,21 +1059,21 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M10">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1082,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-350</v>
+        <v>0.47</v>
       </c>
       <c r="F11">
-        <v>1025</v>
+        <v>0.425</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1094,21 +1097,21 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="L11">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M11">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1120,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-350</v>
+        <v>0.47</v>
       </c>
       <c r="F12">
-        <v>425</v>
+        <v>-0.175</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1132,21 +1135,21 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="L12">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M12">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1158,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-350</v>
+        <v>0.47</v>
       </c>
       <c r="F13">
-        <v>-175</v>
+        <v>-0.775</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1170,21 +1173,21 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="L13">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M13">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1196,10 +1199,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-350</v>
+        <v>-0.03</v>
       </c>
       <c r="F14">
-        <v>-775</v>
+        <v>1.025</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1208,21 +1211,21 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="L14">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M14">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1234,10 +1237,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-1350</v>
+        <v>-0.03</v>
       </c>
       <c r="F15">
-        <v>1025</v>
+        <v>0.425</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1246,21 +1249,21 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="L15">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1272,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-1350</v>
+        <v>-0.03</v>
       </c>
       <c r="F16">
-        <v>425</v>
+        <v>-0.775</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1284,21 +1287,21 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="L16">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1310,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-1350</v>
+        <v>-0.03</v>
       </c>
       <c r="F17">
-        <v>-175</v>
+        <v>-0.175</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1322,21 +1325,21 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="L17">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1348,10 +1351,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-1350</v>
+        <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>-775</v>
+        <v>0.425</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1360,21 +1363,21 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="L18">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M18">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1386,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>490</v>
+        <v>-0.35</v>
       </c>
       <c r="F19">
-        <v>1025</v>
+        <v>-0.175</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1398,21 +1401,21 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="L19">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M19">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1424,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>935</v>
+        <v>-0.35</v>
       </c>
       <c r="F20">
-        <v>-775</v>
+        <v>-0.775</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1436,21 +1439,21 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="L20">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M20">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1462,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>935</v>
+        <v>-1.35</v>
       </c>
       <c r="F21">
-        <v>-175</v>
+        <v>1.025</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1474,21 +1477,21 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="L21">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M21">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1500,10 +1503,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>935</v>
+        <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>425</v>
+        <v>0.425</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1512,21 +1515,21 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
       <c r="L22">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M22">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1538,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>935</v>
+        <v>-1.35</v>
       </c>
       <c r="F23">
-        <v>1025</v>
+        <v>-0.175</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1550,21 +1553,21 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="L23">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M23">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1576,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>490</v>
+        <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>1025</v>
+        <v>-0.775</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1588,21 +1591,21 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="L24">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M24">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1614,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>490</v>
+        <v>-0.35</v>
       </c>
       <c r="F25">
-        <v>-175</v>
+        <v>1.025</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1626,16 +1629,16 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="L25">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M25">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1649,13 +1652,13 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>-2760</v>
+        <v>-2.76</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="F26">
-        <v>-775</v>
+        <v>-0.775</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1664,21 +1667,21 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="L26">
-        <v>1340</v>
+        <v>1.34</v>
       </c>
       <c r="M26">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1687,13 +1690,13 @@
         <v>40</v>
       </c>
       <c r="D27">
-        <v>-2760</v>
+        <v>-2.76</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>-0.5</v>
       </c>
       <c r="F27">
-        <v>-175</v>
+        <v>-0.775</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1702,21 +1705,21 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
       <c r="L27">
-        <v>1340</v>
+        <v>1.34</v>
       </c>
       <c r="M27">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>238</v>
+        <v>190</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1725,13 +1728,13 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>-2760</v>
+        <v>-2.76</v>
       </c>
       <c r="E28">
-        <v>150</v>
+        <v>0.1</v>
       </c>
       <c r="F28">
-        <v>1025</v>
+        <v>-0.175</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1740,21 +1743,21 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J28">
         <v>1</v>
       </c>
       <c r="L28">
-        <v>1340</v>
+        <v>1.34</v>
       </c>
       <c r="M28">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1763,13 +1766,13 @@
         <v>42</v>
       </c>
       <c r="D29">
-        <v>-2760</v>
+        <v>-2.76</v>
       </c>
       <c r="E29">
-        <v>150</v>
+        <v>-0.5</v>
       </c>
       <c r="F29">
-        <v>425</v>
+        <v>-0.175</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1778,21 +1781,21 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J29">
         <v>1</v>
       </c>
       <c r="L29">
-        <v>1340</v>
+        <v>1.34</v>
       </c>
       <c r="M29">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1801,36 +1804,36 @@
         <v>43</v>
       </c>
       <c r="D30">
-        <v>-2760</v>
+        <v>1.2</v>
       </c>
       <c r="E30">
-        <v>-500</v>
+        <v>0.445</v>
       </c>
       <c r="F30">
-        <v>-775</v>
+        <v>-0.175</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="L30">
-        <v>1340</v>
+        <v>0.96</v>
       </c>
       <c r="M30">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1839,36 +1842,36 @@
         <v>44</v>
       </c>
       <c r="D31">
-        <v>-2760</v>
+        <v>1.2</v>
       </c>
       <c r="E31">
-        <v>-500</v>
+        <v>0.445</v>
       </c>
       <c r="F31">
-        <v>-175</v>
+        <v>1.025</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>1340</v>
+        <v>0.96</v>
       </c>
       <c r="M31">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -1877,13 +1880,13 @@
         <v>45</v>
       </c>
       <c r="D32">
-        <v>1200</v>
+        <v>1.2</v>
       </c>
       <c r="E32">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>-175</v>
+        <v>1.025</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -1892,21 +1895,21 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="L32">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -1915,13 +1918,13 @@
         <v>46</v>
       </c>
       <c r="D33">
-        <v>1200</v>
+        <v>1.2</v>
       </c>
       <c r="E33">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1025</v>
+        <v>-0.175</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1930,21 +1933,21 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="L33">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -1953,13 +1956,13 @@
         <v>47</v>
       </c>
       <c r="D34">
-        <v>1200</v>
+        <v>1.2</v>
       </c>
       <c r="E34">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>425</v>
+        <v>0.425</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1968,21 +1971,21 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="L34">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="M34">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -1991,13 +1994,13 @@
         <v>48</v>
       </c>
       <c r="D35">
-        <v>1200</v>
+        <v>1.2</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>-175</v>
+        <v>1.025</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2006,21 +2009,21 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="L35">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="M35">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2029,13 +2032,13 @@
         <v>49</v>
       </c>
       <c r="D36">
-        <v>1200</v>
+        <v>1.2</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="F36">
-        <v>425</v>
+        <v>-0.775</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2044,21 +2047,21 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="L36">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="M36">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2067,13 +2070,13 @@
         <v>50</v>
       </c>
       <c r="D37">
-        <v>1200</v>
+        <v>1.2</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="F37">
-        <v>1025</v>
+        <v>0.425</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2082,21 +2085,21 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="L37">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="M37">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2105,36 +2108,36 @@
         <v>51</v>
       </c>
       <c r="D38">
-        <v>1200</v>
+        <v>0.96</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F38">
-        <v>1025</v>
+        <v>-0.775</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="L38">
-        <v>960</v>
+        <v>0.592</v>
       </c>
       <c r="M38">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2143,36 +2146,36 @@
         <v>52</v>
       </c>
       <c r="D39">
-        <v>1200</v>
+        <v>0.96</v>
       </c>
       <c r="E39">
-        <v>445</v>
+        <v>-0.3</v>
       </c>
       <c r="F39">
-        <v>-775</v>
+        <v>1.025</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>960</v>
+        <v>0.592</v>
       </c>
       <c r="M39">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2181,13 +2184,13 @@
         <v>53</v>
       </c>
       <c r="D40">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="E40">
-        <v>-300</v>
+        <v>-0.3</v>
       </c>
       <c r="F40">
-        <v>-775</v>
+        <v>0.425</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -2196,21 +2199,21 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>592</v>
+        <v>0.592</v>
       </c>
       <c r="M40">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2219,13 +2222,13 @@
         <v>54</v>
       </c>
       <c r="D41">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="E41">
-        <v>-300</v>
+        <v>-0.3</v>
       </c>
       <c r="F41">
-        <v>1025</v>
+        <v>-0.175</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -2234,21 +2237,21 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>592</v>
+        <v>0.592</v>
       </c>
       <c r="M41">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2257,36 +2260,36 @@
         <v>55</v>
       </c>
       <c r="D42">
-        <v>960</v>
+        <v>0.6</v>
       </c>
       <c r="E42">
-        <v>-300</v>
+        <v>-0.45</v>
       </c>
       <c r="F42">
-        <v>-175</v>
+        <v>-0.025</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>592</v>
+        <v>1.94</v>
       </c>
       <c r="M42">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2295,36 +2298,36 @@
         <v>56</v>
       </c>
       <c r="D43">
-        <v>960</v>
+        <v>0.6</v>
       </c>
       <c r="E43">
-        <v>-300</v>
+        <v>0.15</v>
       </c>
       <c r="F43">
-        <v>425</v>
+        <v>-0.775</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>592</v>
+        <v>1.94</v>
       </c>
       <c r="M43">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2333,13 +2336,13 @@
         <v>57</v>
       </c>
       <c r="D44">
-        <v>600</v>
+        <v>0.6</v>
       </c>
       <c r="E44">
-        <v>750</v>
+        <v>-0.45</v>
       </c>
       <c r="F44">
-        <v>-25</v>
+        <v>-0.775</v>
       </c>
       <c r="G44">
         <v>5</v>
@@ -2348,16 +2351,16 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M44">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2371,13 +2374,13 @@
         <v>58</v>
       </c>
       <c r="D45">
-        <v>600</v>
+        <v>0.6</v>
       </c>
       <c r="E45">
-        <v>150</v>
+        <v>0.15</v>
       </c>
       <c r="F45">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G45">
         <v>5</v>
@@ -2386,21 +2389,21 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M45">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2409,13 +2412,13 @@
         <v>59</v>
       </c>
       <c r="D46">
-        <v>600</v>
+        <v>0.6</v>
       </c>
       <c r="E46">
-        <v>150</v>
+        <v>0.75</v>
       </c>
       <c r="F46">
-        <v>-775</v>
+        <v>-0.025</v>
       </c>
       <c r="G46">
         <v>5</v>
@@ -2424,21 +2427,21 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M46">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2447,13 +2450,13 @@
         <v>60</v>
       </c>
       <c r="D47">
-        <v>600</v>
+        <v>0.6</v>
       </c>
       <c r="E47">
-        <v>-450</v>
+        <v>0.75</v>
       </c>
       <c r="F47">
-        <v>-25</v>
+        <v>-0.775</v>
       </c>
       <c r="G47">
         <v>5</v>
@@ -2462,21 +2465,21 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M47">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2485,13 +2488,13 @@
         <v>61</v>
       </c>
       <c r="D48">
-        <v>600</v>
+        <v>0.6</v>
       </c>
       <c r="E48">
-        <v>-450</v>
+        <v>-0.9</v>
       </c>
       <c r="F48">
-        <v>-775</v>
+        <v>-0.025</v>
       </c>
       <c r="G48">
         <v>5</v>
@@ -2500,21 +2503,21 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M48">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2523,13 +2526,13 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>600</v>
+        <v>0.6</v>
       </c>
       <c r="E49">
-        <v>-900</v>
+        <v>-0.9</v>
       </c>
       <c r="F49">
-        <v>-25</v>
+        <v>-0.775</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -2538,21 +2541,21 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M49">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2561,13 +2564,13 @@
         <v>63</v>
       </c>
       <c r="D50">
-        <v>600</v>
+        <v>0.3</v>
       </c>
       <c r="E50">
-        <v>-900</v>
+        <v>-0.9</v>
       </c>
       <c r="F50">
-        <v>-775</v>
+        <v>0.425</v>
       </c>
       <c r="G50">
         <v>5</v>
@@ -2576,21 +2579,21 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M50">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2599,13 +2602,13 @@
         <v>64</v>
       </c>
       <c r="D51">
-        <v>600</v>
+        <v>0.3</v>
       </c>
       <c r="E51">
-        <v>750</v>
+        <v>-0.9</v>
       </c>
       <c r="F51">
-        <v>-775</v>
+        <v>-0.175</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -2614,21 +2617,21 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M51">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2637,13 +2640,13 @@
         <v>65</v>
       </c>
       <c r="D52">
-        <v>300</v>
+        <v>0.3</v>
       </c>
       <c r="E52">
-        <v>-900</v>
+        <v>-0.9</v>
       </c>
       <c r="F52">
-        <v>425</v>
+        <v>-0.775</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -2652,16 +2655,16 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M52">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2675,13 +2678,13 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>300</v>
+        <v>0.3</v>
       </c>
       <c r="E53">
-        <v>-900</v>
+        <v>-0.9</v>
       </c>
       <c r="F53">
-        <v>1025</v>
+        <v>1.025</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -2690,21 +2693,21 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M53">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2713,36 +2716,36 @@
         <v>67</v>
       </c>
       <c r="D54">
-        <v>300</v>
+        <v>1.8</v>
       </c>
       <c r="E54">
-        <v>-900</v>
+        <v>0.3</v>
       </c>
       <c r="F54">
-        <v>-775</v>
+        <v>1.05</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="L54">
-        <v>1940</v>
+        <v>1.932</v>
       </c>
       <c r="M54">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2751,36 +2754,36 @@
         <v>68</v>
       </c>
       <c r="D55">
-        <v>300</v>
+        <v>1.8</v>
       </c>
       <c r="E55">
-        <v>-900</v>
+        <v>0.3</v>
       </c>
       <c r="F55">
-        <v>-175</v>
+        <v>0.45</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J55">
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1940</v>
+        <v>1.932</v>
       </c>
       <c r="M55">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2789,13 +2792,13 @@
         <v>69</v>
       </c>
       <c r="D56">
-        <v>1800</v>
+        <v>1.8</v>
       </c>
       <c r="E56">
-        <v>300</v>
+        <v>0.3</v>
       </c>
       <c r="F56">
-        <v>1050</v>
+        <v>-0.75</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -2804,16 +2807,16 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
       <c r="M56">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2827,13 +2830,13 @@
         <v>70</v>
       </c>
       <c r="D57">
-        <v>1800</v>
+        <v>1.8</v>
       </c>
       <c r="E57">
-        <v>300</v>
+        <v>0.3</v>
       </c>
       <c r="F57">
-        <v>-150</v>
+        <v>-0.15</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2842,21 +2845,21 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="L57">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
       <c r="M57">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2865,13 +2868,13 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>1800</v>
+        <v>1.8</v>
       </c>
       <c r="E58">
-        <v>300</v>
+        <v>-0.3</v>
       </c>
       <c r="F58">
-        <v>450</v>
+        <v>0.45</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -2880,21 +2883,21 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
       <c r="M58">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -2903,13 +2906,13 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>1800</v>
+        <v>1.8</v>
       </c>
       <c r="E59">
-        <v>-300</v>
+        <v>-0.3</v>
       </c>
       <c r="F59">
-        <v>1050</v>
+        <v>-0.15</v>
       </c>
       <c r="G59">
         <v>6</v>
@@ -2918,21 +2921,21 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
       <c r="M59">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -2941,13 +2944,13 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>1800</v>
+        <v>1.8</v>
       </c>
       <c r="E60">
-        <v>-300</v>
+        <v>-0.3</v>
       </c>
       <c r="F60">
-        <v>450</v>
+        <v>-0.75</v>
       </c>
       <c r="G60">
         <v>6</v>
@@ -2956,21 +2959,21 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
       <c r="M60">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -2979,13 +2982,13 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>1800</v>
+        <v>1.8</v>
       </c>
       <c r="E61">
-        <v>-300</v>
+        <v>-0.3</v>
       </c>
       <c r="F61">
-        <v>-150</v>
+        <v>1.05</v>
       </c>
       <c r="G61">
         <v>6</v>
@@ -2994,21 +2997,21 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
       <c r="M61">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3017,36 +3020,36 @@
         <v>75</v>
       </c>
       <c r="D62">
-        <v>1800</v>
+        <v>0.72</v>
       </c>
       <c r="E62">
-        <v>-300</v>
+        <v>0.6</v>
       </c>
       <c r="F62">
-        <v>-750</v>
-      </c>
-      <c r="G62">
-        <v>6</v>
+        <v>-0.025</v>
+      </c>
+      <c r="G62" t="s">
+        <v>87</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J62">
         <v>1</v>
       </c>
       <c r="L62">
-        <v>1932</v>
+        <v>2.9</v>
       </c>
       <c r="M62">
-        <v>2655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3055,36 +3058,36 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>1800</v>
+        <v>1.41</v>
       </c>
       <c r="E63">
-        <v>300</v>
+        <v>0.15</v>
       </c>
       <c r="F63">
-        <v>-750</v>
-      </c>
-      <c r="G63">
-        <v>6</v>
+        <v>-0.025</v>
+      </c>
+      <c r="G63" t="s">
+        <v>87</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J63">
         <v>1</v>
       </c>
       <c r="L63">
-        <v>1932</v>
+        <v>2.9</v>
       </c>
       <c r="M63">
-        <v>2655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3093,36 +3096,36 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>720</v>
+        <v>1.41</v>
       </c>
       <c r="E64">
-        <v>1050</v>
+        <v>0.6</v>
       </c>
       <c r="F64">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G64" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J64">
         <v>1</v>
       </c>
       <c r="L64">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M64">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3131,36 +3134,36 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>720</v>
+        <v>1.41</v>
       </c>
       <c r="E65">
-        <v>600</v>
+        <v>1.2</v>
       </c>
       <c r="F65">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G65" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J65">
         <v>1</v>
       </c>
       <c r="L65">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M65">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3169,36 +3172,36 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>720</v>
+        <v>2.31</v>
       </c>
       <c r="E66">
-        <v>150</v>
+        <v>0.15</v>
       </c>
       <c r="F66">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G66" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J66">
         <v>1</v>
       </c>
       <c r="L66">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M66">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="1">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3207,36 +3210,36 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>120</v>
+        <v>2.31</v>
       </c>
       <c r="E67">
-        <v>150</v>
+        <v>0.6</v>
       </c>
       <c r="F67">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G67" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J67">
         <v>1</v>
       </c>
       <c r="L67">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M67">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3245,36 +3248,36 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>120</v>
+        <v>2.31</v>
       </c>
       <c r="E68">
-        <v>600</v>
+        <v>1.2</v>
       </c>
       <c r="F68">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G68" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J68">
         <v>1</v>
       </c>
       <c r="L68">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M68">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="1">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3283,36 +3286,36 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>2310</v>
+        <v>0.12</v>
       </c>
       <c r="E69">
-        <v>1200</v>
+        <v>1.05</v>
       </c>
       <c r="F69">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G69" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J69">
         <v>1</v>
       </c>
       <c r="L69">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M69">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3321,36 +3324,36 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>2310</v>
+        <v>0.12</v>
       </c>
       <c r="E70">
-        <v>600</v>
+        <v>0.6</v>
       </c>
       <c r="F70">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G70" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J70">
         <v>1</v>
       </c>
       <c r="L70">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M70">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3359,36 +3362,36 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>2310</v>
+        <v>0.12</v>
       </c>
       <c r="E71">
-        <v>150</v>
+        <v>0.15</v>
       </c>
       <c r="F71">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G71" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J71">
         <v>1</v>
       </c>
       <c r="L71">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M71">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3397,36 +3400,36 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>1410</v>
+        <v>0.72</v>
       </c>
       <c r="E72">
-        <v>1200</v>
+        <v>0.15</v>
       </c>
       <c r="F72">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G72" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J72">
         <v>1</v>
       </c>
       <c r="L72">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M72">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="1">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
@@ -3435,107 +3438,31 @@
         <v>86</v>
       </c>
       <c r="D73">
-        <v>1410</v>
+        <v>0.72</v>
       </c>
       <c r="E73">
-        <v>150</v>
+        <v>1.05</v>
       </c>
       <c r="F73">
-        <v>-25</v>
+        <v>-0.025</v>
       </c>
       <c r="G73" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J73">
         <v>1</v>
       </c>
       <c r="L73">
-        <v>2900</v>
+        <v>2.9</v>
       </c>
       <c r="M73">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
-      <c r="A74" s="1">
-        <v>231</v>
-      </c>
-      <c r="B74" t="s">
-        <v>14</v>
-      </c>
-      <c r="C74" t="s">
-        <v>87</v>
-      </c>
-      <c r="D74">
-        <v>120</v>
-      </c>
-      <c r="E74">
-        <v>1050</v>
-      </c>
-      <c r="F74">
-        <v>-25</v>
-      </c>
-      <c r="G74" t="s">
-        <v>89</v>
-      </c>
-      <c r="H74">
-        <v>1</v>
-      </c>
-      <c r="I74" t="s">
-        <v>91</v>
-      </c>
-      <c r="J74">
-        <v>1</v>
-      </c>
-      <c r="L74">
-        <v>2900</v>
-      </c>
-      <c r="M74">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
-      <c r="A75" s="1">
-        <v>226</v>
-      </c>
-      <c r="B75" t="s">
-        <v>14</v>
-      </c>
-      <c r="C75" t="s">
-        <v>88</v>
-      </c>
-      <c r="D75">
-        <v>1410</v>
-      </c>
-      <c r="E75">
-        <v>600</v>
-      </c>
-      <c r="F75">
-        <v>-25</v>
-      </c>
-      <c r="G75" t="s">
-        <v>89</v>
-      </c>
-      <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75" t="s">
-        <v>91</v>
-      </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="L75">
-        <v>2900</v>
-      </c>
-      <c r="M75">
-        <v>1932</v>
+        <v>1.932</v>
       </c>
     </row>
   </sheetData>
@@ -3597,19 +3524,19 @@
         <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D2">
-        <v>1202</v>
+        <v>1.202</v>
       </c>
       <c r="E2">
-        <v>160</v>
+        <v>0.16</v>
       </c>
       <c r="F2">
-        <v>-181</v>
+        <v>-0.181</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -3618,16 +3545,16 @@
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="M2">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -3635,19 +3562,19 @@
         <v>146</v>
       </c>
       <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
         <v>92</v>
       </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
       <c r="D3">
-        <v>1200</v>
+        <v>1.2</v>
       </c>
       <c r="E3">
-        <v>210</v>
+        <v>0.21</v>
       </c>
       <c r="F3">
-        <v>-50</v>
+        <v>-0.05</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -3656,36 +3583,36 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>960</v>
+        <v>0.96</v>
       </c>
       <c r="M3">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D4">
-        <v>392</v>
+        <v>0.305</v>
       </c>
       <c r="E4">
-        <v>-575</v>
+        <v>0.45</v>
       </c>
       <c r="F4">
-        <v>-1024</v>
+        <v>-0.453</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3694,36 +3621,36 @@
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M4">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D5">
-        <v>492</v>
+        <v>0.392</v>
       </c>
       <c r="E5">
-        <v>-450</v>
+        <v>-0.575</v>
       </c>
       <c r="F5">
-        <v>-175</v>
+        <v>-1.024</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3732,36 +3659,36 @@
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M5">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D6">
-        <v>540</v>
+        <v>0.492</v>
       </c>
       <c r="E6">
-        <v>450</v>
+        <v>-0.45</v>
       </c>
       <c r="F6">
-        <v>-175</v>
+        <v>-0.175</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3770,36 +3697,36 @@
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M6">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D7">
-        <v>305</v>
+        <v>0.54</v>
       </c>
       <c r="E7">
-        <v>450</v>
+        <v>0.45</v>
       </c>
       <c r="F7">
-        <v>-453</v>
+        <v>-0.175</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3808,36 +3735,36 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M7">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D8">
-        <v>600</v>
+        <v>0.38</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F8">
-        <v>125</v>
+        <v>-0.725</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3846,36 +3773,36 @@
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M8">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D9">
-        <v>380</v>
+        <v>0.6</v>
       </c>
       <c r="E9">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>-725</v>
+        <v>0.125</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3884,16 +3811,16 @@
         <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1940</v>
+        <v>1.94</v>
       </c>
       <c r="M9">
-        <v>2655</v>
+        <v>2.655</v>
       </c>
     </row>
   </sheetData>
@@ -3914,13 +3841,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="103">
   <si>
     <t>Marking type</t>
   </si>
@@ -63,78 +63,78 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2c3:TMP1S2c3:1155203</t>
+  </si>
+  <si>
+    <t>TMP1S2d2:TMP1S2d2:1155209</t>
+  </si>
+  <si>
+    <t>TMP1S2d3:TMP1S2d3:1155208</t>
+  </si>
+  <si>
+    <t>TMP1S2d4:TMP1S2d4:1155207</t>
+  </si>
+  <si>
+    <t>TMP1S2c1:TMP1S2c1:1155205</t>
+  </si>
+  <si>
+    <t>TMP1S2c2:TMP1S2c2:1155204</t>
+  </si>
+  <si>
+    <t>TMP1S2e3:TMP1S2e3:1155213</t>
+  </si>
+  <si>
+    <t>TMP1S2c4:TMP1S2c4:1155202</t>
+  </si>
+  <si>
+    <t>TMP1S2b1:TMP1S2b1:1155200</t>
+  </si>
+  <si>
+    <t>TMP1S2b2:TMP1S2b2:1155199</t>
+  </si>
+  <si>
+    <t>TMP1S2b3:TMP1S2b3:1155198</t>
+  </si>
+  <si>
+    <t>TMP1S2d1:TMP1S2d1:1155210</t>
+  </si>
+  <si>
+    <t>TMP1S2b4:TMP1S2b4:1155197</t>
+  </si>
+  <si>
+    <t>TMP1S2a2:TMP1S2a2:1155194</t>
+  </si>
+  <si>
+    <t>TMP1S2a3:TMP1S2a3:1155193</t>
+  </si>
+  <si>
+    <t>TMP1S2a4:TMP1S2a4:1155192</t>
+  </si>
+  <si>
+    <t>TMP1S2e2:TMP1S2e2:1155214</t>
+  </si>
+  <si>
+    <t>TMP1S2e1:TMP1S2e1:1155215</t>
+  </si>
+  <si>
+    <t>TMP1S2f4:TMP1S2f4:1155217</t>
+  </si>
+  <si>
+    <t>TMP1S2f3:TMP1S2f3:1155218</t>
+  </si>
+  <si>
+    <t>TMP1S2f2:TMP1S2f2:1155219</t>
+  </si>
+  <si>
+    <t>TMP1S2f1:TMP1S2f1:1155220</t>
+  </si>
+  <si>
+    <t>TMP1S2a1:TMP1S2a1:1155195</t>
+  </si>
+  <si>
     <t>TMP1S2e4:TMP1S2e4:1155212</t>
   </si>
   <si>
-    <t>TMP1S2f1:TMP1S2f1:1155220</t>
-  </si>
-  <si>
-    <t>TMP1S2f2:TMP1S2f2:1155219</t>
-  </si>
-  <si>
-    <t>TMP1S2f3:TMP1S2f3:1155218</t>
-  </si>
-  <si>
-    <t>TMP1S2f4:TMP1S2f4:1155217</t>
-  </si>
-  <si>
-    <t>TMP1S2e1:TMP1S2e1:1155215</t>
-  </si>
-  <si>
-    <t>TMP1S2e2:TMP1S2e2:1155214</t>
-  </si>
-  <si>
-    <t>TMP1S2e3:TMP1S2e3:1155213</t>
-  </si>
-  <si>
-    <t>TMP1S2d1:TMP1S2d1:1155210</t>
-  </si>
-  <si>
-    <t>TMP1S2d2:TMP1S2d2:1155209</t>
-  </si>
-  <si>
-    <t>TMP1S2d3:TMP1S2d3:1155208</t>
-  </si>
-  <si>
-    <t>TMP1S2d4:TMP1S2d4:1155207</t>
-  </si>
-  <si>
-    <t>TMP1S2c1:TMP1S2c1:1155205</t>
-  </si>
-  <si>
-    <t>TMP1S2c2:TMP1S2c2:1155204</t>
-  </si>
-  <si>
-    <t>TMP1S2c4:TMP1S2c4:1155202</t>
-  </si>
-  <si>
-    <t>TMP1S2c3:TMP1S2c3:1155203</t>
-  </si>
-  <si>
-    <t>TMP1S2b2:TMP1S2b2:1155199</t>
-  </si>
-  <si>
-    <t>TMP1S2b3:TMP1S2b3:1155198</t>
-  </si>
-  <si>
-    <t>TMP1S2b4:TMP1S2b4:1155197</t>
-  </si>
-  <si>
-    <t>TMP1S2a1:TMP1S2a1:1155195</t>
-  </si>
-  <si>
-    <t>TMP1S2a2:TMP1S2a2:1155194</t>
-  </si>
-  <si>
-    <t>TMP1S2a3:TMP1S2a3:1155193</t>
-  </si>
-  <si>
-    <t>TMP1S2a4:TMP1S2a4:1155192</t>
-  </si>
-  <si>
-    <t>TMP1S2b1:TMP1S2b1:1155200</t>
-  </si>
-  <si>
     <t>TMP2S2b2:TMP2S2b2:1155222</t>
   </si>
   <si>
@@ -147,6 +147,9 @@
     <t>TMP2S2a1:TMP2S2a1:1155225</t>
   </si>
   <si>
+    <t>TMP3S2b4:TMP3S2b4:1155227</t>
+  </si>
+  <si>
     <t>TMP3S2b3:TMP3S2b3:1155228</t>
   </si>
   <si>
@@ -165,117 +168,114 @@
     <t>TMP3S2a1:TMP3S2a1:1155234</t>
   </si>
   <si>
-    <t>TMP3S2b4:TMP3S2b4:1155227</t>
-  </si>
-  <si>
     <t>TMP3S2b2:TMP3S2b2:1155230</t>
   </si>
   <si>
+    <t>TMP4S2b4:TMP4S2b4:1155236</t>
+  </si>
+  <si>
+    <t>TMP4S2a2:TMP4S2a2:1155242</t>
+  </si>
+  <si>
+    <t>TMP4S2a3:TMP4S2a3:1155241</t>
+  </si>
+  <si>
+    <t>TMP4S2b1:TMP4S2b1:1155240</t>
+  </si>
+  <si>
+    <t>TMP4S2b2:TMP4S2b2:1155239</t>
+  </si>
+  <si>
+    <t>TMP4S2b3:TMP4S2b3:1155238</t>
+  </si>
+  <si>
     <t>TMP4S2a4:TMP4S2a4:1155237</t>
   </si>
   <si>
     <t>TMP4S2a1:TMP4S2a1:1155243</t>
   </si>
   <si>
-    <t>TMP4S2a2:TMP4S2a2:1155242</t>
-  </si>
-  <si>
-    <t>TMP4S2a3:TMP4S2a3:1155241</t>
-  </si>
-  <si>
     <t>TMP5S2b3:TMP5S2b3:1155248</t>
   </si>
   <si>
     <t>TMP5S2a2:TMP5S2a2:1155249</t>
   </si>
   <si>
+    <t>TMP5S2b2:TMP5S2b2:1155250</t>
+  </si>
+  <si>
+    <t>TMP5S2b1:TMP5S2b1:1155251</t>
+  </si>
+  <si>
+    <t>TMP5S2a1:TMP5S2a1:1155252</t>
+  </si>
+  <si>
     <t>TMP5S2a3:TMP5S2a3:1155247</t>
   </si>
   <si>
-    <t>TMP5S2b2:TMP5S2b2:1155250</t>
-  </si>
-  <si>
-    <t>TMP5S2b1:TMP5S2b1:1155251</t>
-  </si>
-  <si>
-    <t>TMP5S2a1:TMP5S2a1:1155252</t>
-  </si>
-  <si>
     <t>TMP5S2b4:TMP5S2b4:1155246</t>
   </si>
   <si>
     <t>TMP5S2a4:TMP5S2a4:1155245</t>
   </si>
   <si>
-    <t>TMP4S2b2:TMP4S2b2:1155239</t>
-  </si>
-  <si>
-    <t>TMP4S2b3:TMP4S2b3:1155238</t>
-  </si>
-  <si>
-    <t>TMP4S2b4:TMP4S2b4:1155236</t>
-  </si>
-  <si>
-    <t>TMP4S2b1:TMP4S2b1:1155240</t>
+    <t>TMP6S2a3:TMP6S2a3:1155254</t>
+  </si>
+  <si>
+    <t>TMP6S2a4:TMP6S2a4:1155255</t>
+  </si>
+  <si>
+    <t>TMP6S2a2:TMP6S2a2:1155256</t>
+  </si>
+  <si>
+    <t>TMP6S2a1:TMP6S2a1:1155257</t>
+  </si>
+  <si>
+    <t>TMP6S2b4:TMP6S2b4:1155259</t>
+  </si>
+  <si>
+    <t>TMP6S2b3:TMP6S2b3:1155260</t>
+  </si>
+  <si>
+    <t>TMP6S2b2:TMP6S2b2:1155261</t>
   </si>
   <si>
     <t>TMP6S2b1:TMP6S2b1:1155262</t>
   </si>
   <si>
-    <t>TMP6S2b2:TMP6S2b2:1155261</t>
-  </si>
-  <si>
-    <t>TMP6S2b4:TMP6S2b4:1155259</t>
-  </si>
-  <si>
-    <t>TMP6S2b3:TMP6S2b3:1155260</t>
-  </si>
-  <si>
-    <t>TMP6S2a2:TMP6S2a2:1155256</t>
-  </si>
-  <si>
-    <t>TMP6S2a4:TMP6S2a4:1155255</t>
-  </si>
-  <si>
-    <t>TMP6S2a3:TMP6S2a3:1155254</t>
-  </si>
-  <si>
-    <t>TMP6S2a1:TMP6S2a1:1155257</t>
+    <t>TMP7S2c3:TMP7S2c3:1155274</t>
+  </si>
+  <si>
+    <t>TMP7S2d3:TMP7S2d3:1155273</t>
+  </si>
+  <si>
+    <t>TMP7S2a1:TMP7S2a1:1155269</t>
+  </si>
+  <si>
+    <t>TMP7S2d2:TMP7S2d2:1155272</t>
+  </si>
+  <si>
+    <t>TMP7S2d1:TMP7S2d1:1155271</t>
+  </si>
+  <si>
+    <t>TMP7S2a2:TMP7S2a2:1155268</t>
+  </si>
+  <si>
+    <t>TMP7S2a3:TMP7S2a3:1155267</t>
+  </si>
+  <si>
+    <t>TMP7S2b2:TMP7S2b2:1155265</t>
+  </si>
+  <si>
+    <t>TMP7S2b3:TMP7S2b3:1155264</t>
   </si>
   <si>
     <t>TMP7S2c2:TMP7S2c2:1155275</t>
   </si>
   <si>
-    <t>TMP7S2b3:TMP7S2b3:1155264</t>
-  </si>
-  <si>
-    <t>TMP7S2b2:TMP7S2b2:1155265</t>
-  </si>
-  <si>
     <t>TMP7S2b1:TMP7S2b1:1155266</t>
   </si>
   <si>
-    <t>TMP7S2a3:TMP7S2a3:1155267</t>
-  </si>
-  <si>
-    <t>TMP7S2a2:TMP7S2a2:1155268</t>
-  </si>
-  <si>
-    <t>TMP7S2a1:TMP7S2a1:1155269</t>
-  </si>
-  <si>
-    <t>TMP7S2d1:TMP7S2d1:1155271</t>
-  </si>
-  <si>
-    <t>TMP7S2d2:TMP7S2d2:1155272</t>
-  </si>
-  <si>
-    <t>TMP7S2d3:TMP7S2d3:1155273</t>
-  </si>
-  <si>
-    <t>TMP7S2c3:TMP7S2c3:1155274</t>
-  </si>
-  <si>
     <t>TMP7S2c1:TMP7S2c1:1155276</t>
   </si>
   <si>
@@ -291,6 +291,9 @@
     <t>Fitting</t>
   </si>
   <si>
+    <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
+  </si>
+  <si>
     <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
   </si>
   <si>
@@ -310,9 +313,6 @@
   </si>
   <si>
     <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
   </si>
   <si>
     <t>6</t>
@@ -731,7 +731,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F2">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.9350000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="F3">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -807,7 +807,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -819,10 +819,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.9350000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="F4">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -845,7 +845,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -857,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.9350000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="F5">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -895,10 +895,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F6">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -933,10 +933,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F7">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -974,7 +974,7 @@
         <v>0.49</v>
       </c>
       <c r="F8">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1009,10 +1009,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F9">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.47</v>
+        <v>-0.35</v>
       </c>
       <c r="F10">
         <v>1.025</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.47</v>
+        <v>-0.35</v>
       </c>
       <c r="F11">
         <v>0.425</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.47</v>
+        <v>-0.35</v>
       </c>
       <c r="F12">
         <v>-0.175</v>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1164,7 +1164,7 @@
         <v>0.47</v>
       </c>
       <c r="F13">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1199,10 +1199,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F14">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F15">
         <v>0.425</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F16">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1313,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F17">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1351,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F18">
         <v>0.425</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1389,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F19">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F20">
         <v>-0.775</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1465,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F21">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F22">
         <v>0.425</v>
@@ -1529,7 +1529,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F23">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1582,7 +1582,7 @@
         <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F25">
         <v>1.025</v>
@@ -1652,7 +1652,7 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>-2.76</v>
+        <v>2.76</v>
       </c>
       <c r="E26">
         <v>0.1</v>
@@ -1690,7 +1690,7 @@
         <v>40</v>
       </c>
       <c r="D27">
-        <v>-2.76</v>
+        <v>2.76</v>
       </c>
       <c r="E27">
         <v>-0.5</v>
@@ -1728,7 +1728,7 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>-2.76</v>
+        <v>2.76</v>
       </c>
       <c r="E28">
         <v>0.1</v>
@@ -1766,7 +1766,7 @@
         <v>42</v>
       </c>
       <c r="D29">
-        <v>-2.76</v>
+        <v>2.76</v>
       </c>
       <c r="E29">
         <v>-0.5</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1810,7 +1810,7 @@
         <v>0.445</v>
       </c>
       <c r="F30">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1848,7 +1848,7 @@
         <v>0.445</v>
       </c>
       <c r="F31">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -1883,7 +1883,7 @@
         <v>1.2</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="F32">
         <v>1.025</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2035,10 +2035,10 @@
         <v>1.2</v>
       </c>
       <c r="E36">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2108,10 +2108,10 @@
         <v>51</v>
       </c>
       <c r="D38">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="E38">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>-0.775</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2146,13 +2146,13 @@
         <v>52</v>
       </c>
       <c r="D39">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="E39">
         <v>-0.3</v>
       </c>
       <c r="F39">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G39">
         <v>4</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2184,13 +2184,13 @@
         <v>53</v>
       </c>
       <c r="D40">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="E40">
         <v>-0.3</v>
       </c>
       <c r="F40">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -2213,7 +2213,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2222,13 +2222,13 @@
         <v>54</v>
       </c>
       <c r="D41">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="E41">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -2251,7 +2251,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2260,16 +2260,16 @@
         <v>55</v>
       </c>
       <c r="D42">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E42">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>-0.025</v>
+        <v>0.425</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="L42">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M42">
         <v>2.655</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2298,16 +2298,16 @@
         <v>56</v>
       </c>
       <c r="D43">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E43">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -2319,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="L43">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M43">
         <v>2.655</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2336,16 +2336,16 @@
         <v>57</v>
       </c>
       <c r="D44">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E44">
-        <v>-0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="F44">
         <v>-0.775</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2357,7 +2357,7 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M44">
         <v>2.655</v>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2374,16 +2374,16 @@
         <v>58</v>
       </c>
       <c r="D45">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E45">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="F45">
-        <v>-0.025</v>
+        <v>1.025</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2395,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M45">
         <v>2.655</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2412,10 +2412,10 @@
         <v>59</v>
       </c>
       <c r="D46">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E46">
-        <v>0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="F46">
         <v>-0.025</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2450,10 +2450,10 @@
         <v>60</v>
       </c>
       <c r="D47">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E47">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="F47">
         <v>-0.775</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2488,10 +2488,10 @@
         <v>61</v>
       </c>
       <c r="D48">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E48">
-        <v>-0.9</v>
+        <v>0.15</v>
       </c>
       <c r="F48">
         <v>-0.025</v>
@@ -2517,7 +2517,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2526,13 +2526,13 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E49">
-        <v>-0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F49">
-        <v>-0.775</v>
+        <v>-0.025</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2564,13 +2564,13 @@
         <v>63</v>
       </c>
       <c r="D50">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E50">
-        <v>-0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F50">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G50">
         <v>5</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2602,13 +2602,13 @@
         <v>64</v>
       </c>
       <c r="D51">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E51">
-        <v>-0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="F51">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -2631,7 +2631,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2640,13 +2640,13 @@
         <v>65</v>
       </c>
       <c r="D52">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E52">
         <v>-0.9</v>
       </c>
       <c r="F52">
-        <v>-0.775</v>
+        <v>-0.025</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -2669,7 +2669,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2678,13 +2678,13 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E53">
         <v>-0.9</v>
       </c>
       <c r="F53">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2716,13 +2716,13 @@
         <v>67</v>
       </c>
       <c r="D54">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F54">
-        <v>1.05</v>
+        <v>-0.75</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2754,13 +2754,13 @@
         <v>68</v>
       </c>
       <c r="D55">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F55">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2792,13 +2792,13 @@
         <v>69</v>
       </c>
       <c r="D56">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F56">
-        <v>-0.75</v>
+        <v>0.45</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2830,13 +2830,13 @@
         <v>70</v>
       </c>
       <c r="D57">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F57">
-        <v>-0.15</v>
+        <v>1.05</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2868,13 +2868,13 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F58">
-        <v>0.45</v>
+        <v>-0.75</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -2897,7 +2897,7 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -2906,10 +2906,10 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F59">
         <v>-0.15</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -2944,13 +2944,13 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F60">
-        <v>-0.75</v>
+        <v>0.45</v>
       </c>
       <c r="G60">
         <v>6</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -2982,10 +2982,10 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F61">
         <v>1.05</v>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3023,7 +3023,7 @@
         <v>0.72</v>
       </c>
       <c r="E62">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F62">
         <v>-0.025</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3058,7 +3058,7 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>1.41</v>
+        <v>0.12</v>
       </c>
       <c r="E63">
         <v>0.15</v>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3096,10 +3096,10 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="E64">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F64">
         <v>-0.025</v>
@@ -3125,7 +3125,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3134,10 +3134,10 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>1.41</v>
+        <v>0.12</v>
       </c>
       <c r="E65">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F65">
         <v>-0.025</v>
@@ -3163,7 +3163,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3172,10 +3172,10 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>2.31</v>
+        <v>0.12</v>
       </c>
       <c r="E66">
-        <v>0.15</v>
+        <v>1.05</v>
       </c>
       <c r="F66">
         <v>-0.025</v>
@@ -3239,7 +3239,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3251,7 +3251,7 @@
         <v>2.31</v>
       </c>
       <c r="E68">
-        <v>1.2</v>
+        <v>0.15</v>
       </c>
       <c r="F68">
         <v>-0.025</v>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="1">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3286,10 +3286,10 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>0.12</v>
+        <v>1.41</v>
       </c>
       <c r="E69">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F69">
         <v>-0.025</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3324,10 +3324,10 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>0.12</v>
+        <v>1.41</v>
       </c>
       <c r="E70">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F70">
         <v>-0.025</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3362,10 +3362,10 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E71">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="F71">
         <v>-0.025</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3400,10 +3400,10 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>0.72</v>
+        <v>1.41</v>
       </c>
       <c r="E72">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="F72">
         <v>-0.025</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
         <v>90</v>
@@ -3530,13 +3530,13 @@
         <v>91</v>
       </c>
       <c r="D2">
-        <v>1.202</v>
+        <v>1.8</v>
       </c>
       <c r="E2">
-        <v>0.16</v>
+        <v>1.415</v>
       </c>
       <c r="F2">
-        <v>-0.181</v>
+        <v>0.125</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
         <v>90</v>
@@ -3568,16 +3568,16 @@
         <v>92</v>
       </c>
       <c r="D3">
-        <v>1.2</v>
+        <v>1.202</v>
       </c>
       <c r="E3">
-        <v>0.21</v>
+        <v>-1.255</v>
       </c>
       <c r="F3">
-        <v>-0.05</v>
+        <v>-0.181</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -3589,7 +3589,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M3">
         <v>2.655</v>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
         <v>90</v>
@@ -3606,13 +3606,13 @@
         <v>93</v>
       </c>
       <c r="D4">
-        <v>0.305</v>
+        <v>1.2</v>
       </c>
       <c r="E4">
-        <v>0.45</v>
+        <v>-1.205</v>
       </c>
       <c r="F4">
-        <v>-0.453</v>
+        <v>-0.05</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3635,7 +3635,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>90</v>
@@ -3644,16 +3644,16 @@
         <v>94</v>
       </c>
       <c r="D5">
-        <v>0.392</v>
+        <v>2.31</v>
       </c>
       <c r="E5">
-        <v>-0.575</v>
+        <v>1.505</v>
       </c>
       <c r="F5">
-        <v>-1.024</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
+        <v>0.547</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -3665,15 +3665,15 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
@@ -3682,16 +3682,16 @@
         <v>95</v>
       </c>
       <c r="D6">
-        <v>0.492</v>
+        <v>1.285</v>
       </c>
       <c r="E6">
-        <v>-0.45</v>
+        <v>1.592</v>
       </c>
       <c r="F6">
-        <v>-0.175</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
+        <v>-0.024</v>
+      </c>
+      <c r="G6" t="s">
+        <v>87</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -3703,15 +3703,15 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
         <v>90</v>
@@ -3720,16 +3720,16 @@
         <v>96</v>
       </c>
       <c r="D7">
-        <v>0.54</v>
+        <v>1.41</v>
       </c>
       <c r="E7">
-        <v>0.45</v>
+        <v>1.692</v>
       </c>
       <c r="F7">
-        <v>-0.175</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
+        <v>0.825</v>
+      </c>
+      <c r="G7" t="s">
+        <v>87</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -3741,15 +3741,15 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
@@ -3758,16 +3758,16 @@
         <v>97</v>
       </c>
       <c r="D8">
-        <v>0.38</v>
+        <v>2.31</v>
       </c>
       <c r="E8">
-        <v>-0.8</v>
+        <v>1.74</v>
       </c>
       <c r="F8">
-        <v>-0.725</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
+        <v>0.825</v>
+      </c>
+      <c r="G8" t="s">
+        <v>87</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -3779,15 +3779,15 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B9" t="s">
         <v>90</v>
@@ -3796,16 +3796,16 @@
         <v>98</v>
       </c>
       <c r="D9">
-        <v>0.6</v>
+        <v>1.06</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="F9">
-        <v>0.125</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
+        <v>0.275</v>
+      </c>
+      <c r="G9" t="s">
+        <v>87</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -3817,10 +3817,10 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
   </sheetData>

--- a/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="120">
   <si>
     <t>Marking type</t>
   </si>
@@ -63,112 +63,130 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2d1</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
     <t>TMP1S2c2</t>
   </si>
   <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
+  </si>
+  <si>
+    <t>TMP1S2b1</t>
+  </si>
+  <si>
+    <t>TMP1S2a4</t>
+  </si>
+  <si>
+    <t>TMP1S2a3</t>
+  </si>
+  <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
+    <t>TMP1S2a1</t>
+  </si>
+  <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
     <t>TMP1S2d3</t>
   </si>
   <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2d1</t>
-  </si>
-  <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2b1</t>
-  </si>
-  <si>
-    <t>TMP1S2a3</t>
-  </si>
-  <si>
-    <t>TMP1S2a2</t>
-  </si>
-  <si>
-    <t>TMP1S2a1</t>
-  </si>
-  <si>
-    <t>TMP1S2e3</t>
-  </si>
-  <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2f1</t>
-  </si>
-  <si>
-    <t>TMP1S2f2</t>
-  </si>
-  <si>
-    <t>TMP1S2f3</t>
-  </si>
-  <si>
-    <t>TMP1S2f4</t>
-  </si>
-  <si>
-    <t>TMP1S2a4</t>
-  </si>
-  <si>
-    <t>TMP1S2e1</t>
+    <t>TMP2S2a1</t>
+  </si>
+  <si>
+    <t>TMP2S2a2</t>
+  </si>
+  <si>
+    <t>TMP2S2b1</t>
+  </si>
+  <si>
+    <t>TMP2S2b2</t>
   </si>
   <si>
     <t>TMP2S2c1</t>
   </si>
   <si>
+    <t>TMP2S2c2</t>
+  </si>
+  <si>
     <t>TMP2S2c3</t>
   </si>
   <si>
-    <t>TMP2S2c2</t>
-  </si>
-  <si>
     <t>TMP2S2c4</t>
   </si>
   <si>
+    <t>TMP3S2b3</t>
+  </si>
+  <si>
+    <t>TMP3S2b2</t>
+  </si>
+  <si>
+    <t>TMP3S2b1</t>
+  </si>
+  <si>
+    <t>TMP3S2a4</t>
+  </si>
+  <si>
+    <t>TMP3S2a3</t>
+  </si>
+  <si>
+    <t>TMP3S2a2</t>
+  </si>
+  <si>
     <t>TMP3S2a1</t>
   </si>
   <si>
-    <t>TMP3S2a2</t>
-  </si>
-  <si>
-    <t>TMP3S2a3</t>
-  </si>
-  <si>
-    <t>TMP3S2a4</t>
-  </si>
-  <si>
-    <t>TMP3S2b1</t>
-  </si>
-  <si>
-    <t>TMP3S2b3</t>
-  </si>
-  <si>
     <t>TMP3S2b4</t>
   </si>
   <si>
-    <t>TMP3S2b2</t>
+    <t>TMP4S2a2</t>
+  </si>
+  <si>
+    <t>TMP4S2a1</t>
   </si>
   <si>
     <t>TMP4S2b4</t>
@@ -180,114 +198,108 @@
     <t>TMP4S2b2</t>
   </si>
   <si>
-    <t>TMP4S2a1</t>
-  </si>
-  <si>
-    <t>TMP4S2a2</t>
+    <t>TMP4S2b1</t>
+  </si>
+  <si>
+    <t>TMP4S2a4</t>
   </si>
   <si>
     <t>TMP4S2a3</t>
   </si>
   <si>
-    <t>TMP4S2a4</t>
-  </si>
-  <si>
-    <t>TMP4S2b1</t>
-  </si>
-  <si>
     <t>TMP5S2a4</t>
   </si>
   <si>
+    <t>TMP5S2a1</t>
+  </si>
+  <si>
+    <t>TMP5S2a2</t>
+  </si>
+  <si>
     <t>TMP5S2a3</t>
   </si>
   <si>
-    <t>TMP5S2a2</t>
-  </si>
-  <si>
-    <t>TMP5S2a1</t>
+    <t>TMP6S2b4</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
+  </si>
+  <si>
+    <t>TMP6S2b1</t>
   </si>
   <si>
     <t>TMP6S2a4</t>
   </si>
   <si>
+    <t>TMP6S2a3</t>
+  </si>
+  <si>
+    <t>TMP6S2a2</t>
+  </si>
+  <si>
     <t>TMP6S2a1</t>
   </si>
   <si>
-    <t>TMP6S2a2</t>
-  </si>
-  <si>
-    <t>TMP6S2a3</t>
-  </si>
-  <si>
-    <t>TMP6S2b4</t>
-  </si>
-  <si>
-    <t>TMP6S2b1</t>
-  </si>
-  <si>
-    <t>TMP6S2b2</t>
-  </si>
-  <si>
-    <t>TMP6S2b3</t>
+    <t>TMP7S2d2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
   </si>
   <si>
     <t>TMP7S2b3</t>
   </si>
   <si>
-    <t>TMP7S2b4</t>
-  </si>
-  <si>
-    <t>TMP7S2b5</t>
-  </si>
-  <si>
-    <t>TMP7S2b6</t>
-  </si>
-  <si>
-    <t>TMP7S2b7</t>
-  </si>
-  <si>
-    <t>TMP7S2c1</t>
-  </si>
-  <si>
-    <t>TMP7S2c2</t>
+    <t>TMP7S2a1</t>
+  </si>
+  <si>
+    <t>TMP7S2b1</t>
+  </si>
+  <si>
+    <t>TMP7S2a7</t>
+  </si>
+  <si>
+    <t>TMP7S2a6</t>
+  </si>
+  <si>
+    <t>TMP7S2a5</t>
+  </si>
+  <si>
+    <t>TMP7S2a4</t>
+  </si>
+  <si>
+    <t>TMP7S2a3</t>
+  </si>
+  <si>
+    <t>TMP7S2a2</t>
+  </si>
+  <si>
+    <t>TMP7S2e1</t>
   </si>
   <si>
     <t>TMP7S2b2</t>
   </si>
   <si>
-    <t>TMP7S2d1</t>
-  </si>
-  <si>
-    <t>TMP7S2d2</t>
-  </si>
-  <si>
-    <t>TMP7S2b1</t>
-  </si>
-  <si>
-    <t>TMP7S2a6</t>
-  </si>
-  <si>
-    <t>TMP7S2a5</t>
-  </si>
-  <si>
-    <t>TMP7S2a4</t>
-  </si>
-  <si>
-    <t>TMP7S2a3</t>
-  </si>
-  <si>
-    <t>TMP7S2a2</t>
-  </si>
-  <si>
-    <t>TMP7S2a1</t>
-  </si>
-  <si>
-    <t>TMP7S2e1</t>
-  </si>
-  <si>
-    <t>TMP7S2a7</t>
-  </si>
-  <si>
     <t>TMP7S2e2</t>
   </si>
   <si>
@@ -303,28 +315,55 @@
     <t>Fitting</t>
   </si>
   <si>
+    <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
+  </si>
+  <si>
+    <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
+  </si>
+  <si>
+    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+  </si>
+  <si>
+    <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
+  </si>
+  <si>
+    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+  </si>
+  <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
     <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
   </si>
   <si>
-    <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
-  </si>
-  <si>
-    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
-  </si>
-  <si>
-    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+    <t>BSS.TECE.CONCEALED CISTERN.9370224:BSS.TECE.CONCEALED CISTERN.9370224:1090923</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
   </si>
   <si>
     <t>6</t>
@@ -694,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -743,7 +782,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -758,7 +797,7 @@
         <v>0.47</v>
       </c>
       <c r="F2">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -767,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -781,7 +820,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -796,7 +835,7 @@
         <v>-0.03</v>
       </c>
       <c r="F3">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -805,7 +844,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -819,7 +858,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -834,7 +873,7 @@
         <v>-0.03</v>
       </c>
       <c r="F4">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -843,7 +882,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -857,7 +896,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -869,10 +908,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F5">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -881,7 +920,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -895,7 +934,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -910,7 +949,7 @@
         <v>0.47</v>
       </c>
       <c r="F6">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -919,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -933,7 +972,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -948,7 +987,7 @@
         <v>0.47</v>
       </c>
       <c r="F7">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -957,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -971,7 +1010,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -983,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F8">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -995,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1009,7 +1048,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1021,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F9">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1033,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1047,7 +1086,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1062,7 +1101,7 @@
         <v>0.49</v>
       </c>
       <c r="F10">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1071,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1085,7 +1124,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1100,7 +1139,7 @@
         <v>0.49</v>
       </c>
       <c r="F11">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1109,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1123,7 +1162,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1135,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F12">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1147,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1161,7 +1200,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1173,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-0.03</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F13">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1185,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1199,7 +1238,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1211,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F14">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1223,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1237,7 +1276,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1252,7 +1291,7 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="F15">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1261,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1275,7 +1314,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1287,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.9350000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="F16">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1299,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1313,7 +1352,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1325,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.9350000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="F17">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1337,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1375,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1413,7 +1452,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1451,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1489,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1527,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1565,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1579,7 +1618,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1591,10 +1630,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F24">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1603,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1617,7 +1656,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1629,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F25">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1641,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1667,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="F26">
-        <v>-0.775</v>
+        <v>-0.75</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1679,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1693,7 +1732,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1705,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="F27">
-        <v>0.425</v>
+        <v>-0.15</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1717,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1731,7 +1770,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1743,10 +1782,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F28">
-        <v>-0.175</v>
+        <v>-0.75</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1755,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1781,10 +1820,10 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F29">
-        <v>1.025</v>
+        <v>-0.15</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1793,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1816,28 +1855,28 @@
         <v>43</v>
       </c>
       <c r="D30">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F30">
-        <v>-0.775</v>
+        <v>-0.75</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="L30">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M30">
         <v>2.655</v>
@@ -1854,28 +1893,28 @@
         <v>44</v>
       </c>
       <c r="D31">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F31">
-        <v>-0.175</v>
+        <v>-0.15</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M31">
         <v>2.655</v>
@@ -1892,28 +1931,28 @@
         <v>45</v>
       </c>
       <c r="D32">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F32">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="L32">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M32">
         <v>2.655</v>
@@ -1930,28 +1969,28 @@
         <v>46</v>
       </c>
       <c r="D33">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F33">
-        <v>1.025</v>
+        <v>1.05</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="L33">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M33">
         <v>2.655</v>
@@ -1959,7 +1998,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -1974,7 +2013,7 @@
         <v>0.445</v>
       </c>
       <c r="F34">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1983,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1997,7 +2036,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2012,7 +2051,7 @@
         <v>0.445</v>
       </c>
       <c r="F35">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2021,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2035,7 +2074,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2050,7 +2089,7 @@
         <v>0.445</v>
       </c>
       <c r="F36">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2059,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2073,7 +2112,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2085,10 +2124,10 @@
         <v>0.6</v>
       </c>
       <c r="E37">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2097,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2111,7 +2150,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2120,28 +2159,28 @@
         <v>51</v>
       </c>
       <c r="D38">
+        <v>0.6</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0.425</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>97</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="L38">
         <v>0.96</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>1.025</v>
-      </c>
-      <c r="G38">
-        <v>4</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>93</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="L38">
-        <v>0.592</v>
       </c>
       <c r="M38">
         <v>2.655</v>
@@ -2149,7 +2188,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2158,28 +2197,28 @@
         <v>52</v>
       </c>
       <c r="D39">
+        <v>0.6</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>-0.175</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>97</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="L39">
         <v>0.96</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0.425</v>
-      </c>
-      <c r="G39">
-        <v>4</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>93</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="L39">
-        <v>0.592</v>
       </c>
       <c r="M39">
         <v>2.655</v>
@@ -2187,7 +2226,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2196,28 +2235,28 @@
         <v>53</v>
       </c>
       <c r="D40">
+        <v>0.6</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>-0.775</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>97</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="L40">
         <v>0.96</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>-0.175</v>
-      </c>
-      <c r="G40">
-        <v>4</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>93</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="L40">
-        <v>0.592</v>
       </c>
       <c r="M40">
         <v>2.655</v>
@@ -2225,7 +2264,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2234,28 +2273,28 @@
         <v>54</v>
       </c>
       <c r="D41">
+        <v>0.6</v>
+      </c>
+      <c r="E41">
+        <v>0.445</v>
+      </c>
+      <c r="F41">
+        <v>1.025</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>97</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="L41">
         <v>0.96</v>
-      </c>
-      <c r="E41">
-        <v>-0.3</v>
-      </c>
-      <c r="F41">
-        <v>-0.775</v>
-      </c>
-      <c r="G41">
-        <v>4</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>93</v>
-      </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="L41">
-        <v>0.592</v>
       </c>
       <c r="M41">
         <v>2.655</v>
@@ -2263,7 +2302,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2287,7 +2326,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2301,7 +2340,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2316,7 +2355,7 @@
         <v>-0.3</v>
       </c>
       <c r="F43">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -2325,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2339,7 +2378,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2351,7 +2390,7 @@
         <v>0.96</v>
       </c>
       <c r="E44">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>1.025</v>
@@ -2363,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2377,7 +2416,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2392,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -2401,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2415,7 +2454,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2424,28 +2463,28 @@
         <v>59</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E46">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M46">
         <v>2.655</v>
@@ -2453,7 +2492,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2462,28 +2501,28 @@
         <v>60</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E47">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>-0.775</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M47">
         <v>2.655</v>
@@ -2491,7 +2530,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2500,28 +2539,28 @@
         <v>61</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M48">
         <v>2.655</v>
@@ -2529,7 +2568,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2538,28 +2577,28 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E49">
-        <v>-0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="F49">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M49">
         <v>2.655</v>
@@ -2579,25 +2618,25 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F50">
-        <v>1.05</v>
+        <v>-0.775</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M50">
         <v>2.655</v>
@@ -2617,25 +2656,25 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.3</v>
+        <v>-0.45</v>
       </c>
       <c r="F51">
-        <v>-0.75</v>
+        <v>-0.775</v>
       </c>
       <c r="G51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M51">
         <v>2.655</v>
@@ -2655,25 +2694,25 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>-0.15</v>
+        <v>-0.775</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M52">
         <v>2.655</v>
@@ -2693,25 +2732,25 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F53">
-        <v>0.45</v>
+        <v>-0.775</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M53">
         <v>2.655</v>
@@ -2719,7 +2758,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2734,7 +2773,7 @@
         <v>-0.3</v>
       </c>
       <c r="F54">
-        <v>1.05</v>
+        <v>1.025</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -2743,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2757,7 +2796,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2772,7 +2811,7 @@
         <v>-0.3</v>
       </c>
       <c r="F55">
-        <v>-0.75</v>
+        <v>0.425</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -2781,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2795,7 +2834,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2810,7 +2849,7 @@
         <v>-0.3</v>
       </c>
       <c r="F56">
-        <v>-0.15</v>
+        <v>-0.175</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -2819,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2833,7 +2872,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2848,7 +2887,7 @@
         <v>-0.3</v>
       </c>
       <c r="F57">
-        <v>0.45</v>
+        <v>-0.775</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2857,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2871,7 +2910,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2880,36 +2919,36 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>91</v>
+        <v>1.025</v>
+      </c>
+      <c r="G58">
+        <v>6</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
-        <v>2.9</v>
+        <v>1.932</v>
       </c>
       <c r="M58">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -2918,36 +2957,36 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59" t="s">
-        <v>91</v>
+        <v>0.425</v>
+      </c>
+      <c r="G59">
+        <v>6</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
-        <v>2.9</v>
+        <v>1.932</v>
       </c>
       <c r="M59">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -2956,36 +2995,36 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60" t="s">
-        <v>91</v>
+        <v>-0.175</v>
+      </c>
+      <c r="G60">
+        <v>6</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
-        <v>2.9</v>
+        <v>1.932</v>
       </c>
       <c r="M60">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -2994,36 +3033,36 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61" t="s">
-        <v>91</v>
+        <v>-0.775</v>
+      </c>
+      <c r="G61">
+        <v>6</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>2.9</v>
+        <v>1.932</v>
       </c>
       <c r="M61">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3032,22 +3071,22 @@
         <v>75</v>
       </c>
       <c r="D62">
-        <v>0.72</v>
+        <v>2.01</v>
       </c>
       <c r="E62">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3061,7 +3100,7 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3070,7 +3109,7 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="E63">
         <v>0.6</v>
@@ -3079,13 +3118,13 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3099,7 +3138,7 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3117,13 +3156,13 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3137,7 +3176,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3146,22 +3185,22 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>0.72</v>
+        <v>1.41</v>
       </c>
       <c r="E65">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3175,7 +3214,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3184,22 +3223,22 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>2.01</v>
+        <v>0.72</v>
       </c>
       <c r="E66">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3213,7 +3252,7 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="1">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3222,22 +3261,22 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>2.01</v>
+        <v>0.72</v>
       </c>
       <c r="E67">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3251,7 +3290,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3263,19 +3302,19 @@
         <v>0.72</v>
       </c>
       <c r="E68">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3289,7 +3328,7 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="1">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3298,22 +3337,22 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E69">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3327,7 +3366,7 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3336,22 +3375,22 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E70">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3365,7 +3404,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3377,19 +3416,19 @@
         <v>0.12</v>
       </c>
       <c r="E71">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3403,7 +3442,7 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3412,22 +3451,22 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E72">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3441,7 +3480,7 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="1">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
@@ -3453,19 +3492,19 @@
         <v>0.12</v>
       </c>
       <c r="E73">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3479,7 +3518,7 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="1">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B74" t="s">
         <v>14</v>
@@ -3491,19 +3530,19 @@
         <v>0.12</v>
       </c>
       <c r="E74">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3517,7 +3556,7 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="1">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
@@ -3526,22 +3565,22 @@
         <v>88</v>
       </c>
       <c r="D75">
-        <v>2.61</v>
+        <v>0.12</v>
       </c>
       <c r="E75">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3555,7 +3594,7 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="1">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B76" t="s">
         <v>14</v>
@@ -3567,19 +3606,19 @@
         <v>0.12</v>
       </c>
       <c r="E76">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3593,7 +3632,7 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="1">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B77" t="s">
         <v>14</v>
@@ -3602,22 +3641,22 @@
         <v>90</v>
       </c>
       <c r="D77">
-        <v>2.61</v>
+        <v>0.12</v>
       </c>
       <c r="E77">
-        <v>1.2</v>
+        <v>0.45</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3626,6 +3665,158 @@
         <v>2.9</v>
       </c>
       <c r="M77">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" s="1">
+        <v>226</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78">
+        <v>0.12</v>
+      </c>
+      <c r="E78">
+        <v>0.3</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>95</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>97</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>2.9</v>
+      </c>
+      <c r="M78">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" s="1">
+        <v>243</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79" t="s">
+        <v>92</v>
+      </c>
+      <c r="D79">
+        <v>2.61</v>
+      </c>
+      <c r="E79">
+        <v>0.6</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>95</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>97</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>2.9</v>
+      </c>
+      <c r="M79">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" s="1">
+        <v>233</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80">
+        <v>0.72</v>
+      </c>
+      <c r="E80">
+        <v>0.3</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>95</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80" t="s">
+        <v>97</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>2.9</v>
+      </c>
+      <c r="M80">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="1">
+        <v>244</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" t="s">
+        <v>94</v>
+      </c>
+      <c r="D81">
+        <v>2.61</v>
+      </c>
+      <c r="E81">
+        <v>1.2</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
+        <v>95</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>97</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>2.9</v>
+      </c>
+      <c r="M81">
         <v>1.932</v>
       </c>
     </row>
@@ -3636,7 +3827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -3685,37 +3876,37 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1.415</v>
+        <v>0.06</v>
       </c>
       <c r="F2">
-        <v>0.125</v>
+        <v>0.175</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>0.96</v>
+        <v>2.9</v>
       </c>
       <c r="M2">
         <v>2.655</v>
@@ -3726,34 +3917,34 @@
         <v>164</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>0.6</v>
       </c>
       <c r="E3">
-        <v>-1.392</v>
+        <v>0.023</v>
       </c>
       <c r="F3">
         <v>0.387</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M3">
         <v>2.655</v>
@@ -3764,34 +3955,34 @@
         <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D4">
         <v>0.6</v>
       </c>
       <c r="E4">
-        <v>-1.205</v>
+        <v>0.21</v>
       </c>
       <c r="F4">
         <v>-0.05</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M4">
         <v>2.655</v>
@@ -3799,192 +3990,534 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D5">
-        <v>2.31</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E5">
-        <v>1.505</v>
+        <v>0.243</v>
       </c>
       <c r="F5">
-        <v>0.547</v>
-      </c>
-      <c r="G5" t="s">
-        <v>91</v>
+        <v>-0.8</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2.9</v>
+        <v>0.592</v>
       </c>
       <c r="M5">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D6">
-        <v>1.285</v>
+        <v>0.86</v>
       </c>
       <c r="E6">
-        <v>1.592</v>
+        <v>0.508</v>
       </c>
       <c r="F6">
-        <v>-0.024</v>
-      </c>
-      <c r="G6" t="s">
-        <v>91</v>
+        <v>1.468</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2.9</v>
+        <v>0.592</v>
       </c>
       <c r="M6">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D7">
-        <v>1.41</v>
+        <v>0.96</v>
       </c>
       <c r="E7">
-        <v>1.692</v>
+        <v>-0.17</v>
       </c>
       <c r="F7">
-        <v>0.825</v>
-      </c>
-      <c r="G7" t="s">
-        <v>91</v>
+        <v>-0.375</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>2.9</v>
+        <v>0.592</v>
       </c>
       <c r="M7">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D8">
-        <v>2.31</v>
+        <v>0.295</v>
       </c>
       <c r="E8">
-        <v>1.74</v>
+        <v>0.45</v>
       </c>
       <c r="F8">
-        <v>0.825</v>
-      </c>
-      <c r="G8" t="s">
-        <v>91</v>
+        <v>-0.453</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M8">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
+        <v>158</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9">
+        <v>0.208</v>
+      </c>
+      <c r="E9">
+        <v>-0.575</v>
+      </c>
+      <c r="F9">
+        <v>-1.024</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1.94</v>
+      </c>
+      <c r="M9">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="1">
+        <v>153</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10">
+        <v>0.108</v>
+      </c>
+      <c r="E10">
+        <v>-0.45</v>
+      </c>
+      <c r="F10">
+        <v>-0.175</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1.94</v>
+      </c>
+      <c r="M10">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="1">
+        <v>145</v>
+      </c>
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11">
+        <v>0.06</v>
+      </c>
+      <c r="E11">
+        <v>0.45</v>
+      </c>
+      <c r="F11">
+        <v>-0.175</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1.94</v>
+      </c>
+      <c r="M11">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="1">
         <v>144</v>
       </c>
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9">
-        <v>1.06</v>
-      </c>
-      <c r="E9">
-        <v>1.58</v>
-      </c>
-      <c r="F9">
-        <v>0.275</v>
-      </c>
-      <c r="G9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12">
+        <v>0.22</v>
+      </c>
+      <c r="E12">
+        <v>-0.8</v>
+      </c>
+      <c r="F12">
+        <v>-0.725</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1.94</v>
+      </c>
+      <c r="M12">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="1">
+        <v>143</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0.125</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1.94</v>
+      </c>
+      <c r="M13">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="1">
+        <v>139</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E14">
+        <v>-0.705</v>
+      </c>
+      <c r="F14">
+        <v>-1.2</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1.94</v>
+      </c>
+      <c r="M14">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="1">
         <v>103</v>
       </c>
-      <c r="I9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>2.9</v>
-      </c>
-      <c r="M9">
-        <v>1.932</v>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15">
+        <v>0.435</v>
+      </c>
+      <c r="E15">
+        <v>-1.28</v>
+      </c>
+      <c r="F15">
+        <v>-0.79</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1.94</v>
+      </c>
+      <c r="M15">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="1">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16">
+        <v>-0.037</v>
+      </c>
+      <c r="E16">
+        <v>-0.8</v>
+      </c>
+      <c r="F16">
+        <v>-0.365</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" t="s">
+        <v>97</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1.94</v>
+      </c>
+      <c r="M16">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="1">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17">
+        <v>0.09</v>
+      </c>
+      <c r="E17">
+        <v>0.525</v>
+      </c>
+      <c r="F17">
+        <v>-0.825</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1.94</v>
+      </c>
+      <c r="M17">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="1">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18">
+        <v>0.15</v>
+      </c>
+      <c r="E18">
+        <v>0.375</v>
+      </c>
+      <c r="F18">
+        <v>-0.9</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1.94</v>
+      </c>
+      <c r="M18">
+        <v>2.655</v>
       </c>
     </row>
   </sheetData>
@@ -4005,13 +4538,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="J18" t="n">

--- a/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -518,14 +518,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TMP1S2c4</t>
+          <t>TMP1S2b4</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F2" t="n">
         <v>1.025</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -567,17 +567,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TMP1S2d1</t>
+          <t>TMP1S2a4</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -616,17 +616,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TMP1S2d4</t>
+          <t>TMP1S2b1</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03</v>
+        <v>0.49</v>
       </c>
       <c r="F4" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TMP1S2c3</t>
+          <t>TMP1S2b2</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F5" t="n">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -714,17 +714,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TMP1S2c2</t>
+          <t>TMP1S2b3</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -763,17 +763,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TMP1S2c1</t>
+          <t>TMP1S2f3</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.47</v>
+        <v>-1.35</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TMP1S2b4</t>
+          <t>TMP1S2c1</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F8" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -861,17 +861,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TMP1S2b3</t>
+          <t>TMP1S2c2</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F9" t="n">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -910,17 +910,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TMP1S2b2</t>
+          <t>TMP1S2c3</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -959,17 +959,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TMP1S2b1</t>
+          <t>TMP1S2c4</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TMP1S2a4</t>
+          <t>TMP1S2d1</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F12" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1057,17 +1057,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TMP1S2a3</t>
+          <t>TMP1S2d2</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F13" t="n">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TMP1S2a2</t>
+          <t>TMP1S2d3</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TMP1S2a1</t>
+          <t>TMP1S2d4</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1400,17 +1400,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TMP1S2f1</t>
+          <t>TMP1S2a3</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TMP1S2f2</t>
+          <t>TMP1S2f1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1459,7 +1459,7 @@
         <v>-1.35</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TMP1S2f3</t>
+          <t>TMP1S2a2</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1547,17 +1547,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TMP1S2f4</t>
+          <t>TMP1S2a1</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1596,17 +1596,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TMP1S2d2</t>
+          <t>TMP1S2f4</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TMP1S2d3</t>
+          <t>TMP1S2f2</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F25" t="n">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TMP2S2a1</t>
+          <t>TMP2S2a2</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1704,7 +1704,7 @@
         <v>-0.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TMP2S2a2</t>
+          <t>TMP2S2b1</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TMP2S2b1</t>
+          <t>TMP2S2b2</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1802,7 +1802,7 @@
         <v>0.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TMP2S2b2</t>
+          <t>TMP2S2a1</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TMP2S2c1</t>
+          <t>TMP3S2a1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.75</v>
+        <v>-0.775</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M30" t="n">
         <v>2.655</v>
@@ -1930,7 +1930,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1939,21 +1939,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TMP2S2c2</t>
+          <t>TMP3S2a2</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E31" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.15</v>
+        <v>-0.175</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M31" t="n">
         <v>2.655</v>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1988,21 +1988,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TMP2S2c3</t>
+          <t>TMP3S2a3</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E32" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.45</v>
+        <v>0.425</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M32" t="n">
         <v>2.655</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TMP2S2c4</t>
+          <t>TMP3S2a4</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E33" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1.05</v>
+        <v>1.025</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M33" t="n">
         <v>2.655</v>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TMP3S2b3</t>
+          <t>TMP4S2a4</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E34" t="n">
-        <v>0.445</v>
+        <v>-0.3</v>
       </c>
       <c r="F34" t="n">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M34" t="n">
         <v>2.655</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TMP3S2b2</t>
+          <t>TMP4S2a2</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E35" t="n">
-        <v>0.445</v>
+        <v>-0.3</v>
       </c>
       <c r="F35" t="n">
         <v>-0.175</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M35" t="n">
         <v>2.655</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TMP3S2b1</t>
+          <t>TMP4S2a1</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E36" t="n">
-        <v>0.445</v>
+        <v>-0.3</v>
       </c>
       <c r="F36" t="n">
         <v>-0.775</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M36" t="n">
         <v>2.655</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TMP3S2a4</t>
+          <t>TMP4S2a3</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F37" t="n">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M37" t="n">
         <v>2.655</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TMP3S2a3</t>
+          <t>TMP5S2a1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="F38" t="n">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M38" t="n">
         <v>2.655</v>
@@ -2331,21 +2331,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TMP3S2a2</t>
+          <t>TMP5S2a2</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M39" t="n">
         <v>2.655</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2380,21 +2380,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TMP3S2a1</t>
+          <t>TMP5S2a3</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="F40" t="n">
         <v>-0.775</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M40" t="n">
         <v>2.655</v>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2429,21 +2429,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TMP3S2b4</t>
+          <t>TMP6S2a1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.445</v>
+        <v>0.3</v>
       </c>
       <c r="F41" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>0.96</v>
+        <v>1.932</v>
       </c>
       <c r="M41" t="n">
         <v>2.655</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TMP4S2a2</t>
+          <t>TMP6S2a2</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F42" t="n">
         <v>-0.175</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M42" t="n">
         <v>2.655</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TMP4S2a1</t>
+          <t>TMP6S2a3</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M43" t="n">
         <v>2.655</v>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TMP4S2b4</t>
+          <t>TMP6S2a4</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F44" t="n">
         <v>1.025</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M44" t="n">
         <v>2.655</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2625,21 +2625,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TMP4S2b3</t>
+          <t>TMP6S2b1</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M45" t="n">
         <v>2.655</v>
@@ -2665,7 +2665,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2674,21 +2674,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TMP4S2b2</t>
+          <t>TMP6S2b2</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F46" t="n">
         <v>-0.175</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M46" t="n">
         <v>2.655</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TMP4S2b1</t>
+          <t>TMP6S2b3</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M47" t="n">
         <v>2.655</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2772,11 +2772,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TMP4S2a4</t>
+          <t>TMP6S2b4</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>-0.3</v>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M48" t="n">
         <v>2.655</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TMP4S2a3</t>
+          <t>TMP7S2a7</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.96</v>
+        <v>0.12</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.3</v>
+        <v>1.05</v>
       </c>
       <c r="F49" t="n">
-        <v>0.425</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>0.592</v>
+        <v>2.9</v>
       </c>
       <c r="M49" t="n">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TMP5S2a4</t>
+          <t>TMP7S2a1</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9</v>
+        <v>0.15</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M50" t="n">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TMP5S2a1</t>
+          <t>TMP7S2a2</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -2949,17 +2949,17 @@
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M51" t="n">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2968,21 +2968,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TMP5S2a2</t>
+          <t>TMP7S2a3</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2998,10 +2998,10 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M52" t="n">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -3017,21 +3017,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TMP5S2a3</t>
+          <t>TMP7S2b1</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E53" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M53" t="n">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3066,21 +3066,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TMP6S2b4</t>
+          <t>TMP7S2b2</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F54" t="n">
-        <v>1.025</v>
+        <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M54" t="n">
         <v>1.932</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.655</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TMP6S2b3</t>
+          <t>TMP7S2b3</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F55" t="n">
-        <v>0.425</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M55" t="n">
         <v>1.932</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.655</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TMP6S2b2</t>
+          <t>TMP7S2b4</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.175</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -3194,17 +3194,17 @@
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M56" t="n">
         <v>1.932</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.655</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3213,21 +3213,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TMP6S2b1</t>
+          <t>TMP7S2b5</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3</v>
+        <v>0.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -3243,10 +3243,10 @@
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M57" t="n">
         <v>1.932</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2.655</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -3262,21 +3262,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TMP6S2a4</t>
+          <t>TMP7S2b6</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F58" t="n">
-        <v>1.025</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -3292,17 +3292,17 @@
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M58" t="n">
         <v>1.932</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2.655</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TMP6S2a3</t>
+          <t>TMP7S2a6</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F59" t="n">
-        <v>0.425</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M59" t="n">
         <v>1.932</v>
-      </c>
-      <c r="M59" t="n">
-        <v>2.655</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3360,21 +3360,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TMP6S2a2</t>
+          <t>TMP7S2b7</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.175</v>
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -3390,17 +3390,17 @@
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M60" t="n">
         <v>1.932</v>
-      </c>
-      <c r="M60" t="n">
-        <v>2.655</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3409,21 +3409,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TMP6S2a1</t>
+          <t>TMP7S2c2</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -3439,17 +3439,17 @@
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M61" t="n">
         <v>1.932</v>
-      </c>
-      <c r="M61" t="n">
-        <v>2.655</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3458,14 +3458,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TMP7S2d2</t>
+          <t>TMP7S2d1</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>2.01</v>
       </c>
       <c r="E62" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3507,14 +3507,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TMP7S2d1</t>
+          <t>TMP7S2d2</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>2.01</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3556,14 +3556,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TMP7S2c2</t>
+          <t>TMP7S2e1</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.41</v>
+        <v>2.61</v>
       </c>
       <c r="E64" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3605,14 +3605,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TMP7S2c1</t>
+          <t>TMP7S2e2</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.41</v>
+        <v>2.61</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3654,14 +3654,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TMP7S2b7</t>
+          <t>TMP7S2a4</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E66" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3703,14 +3703,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TMP7S2b6</t>
+          <t>TMP7S2a5</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3752,14 +3752,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TMP7S2b5</t>
+          <t>TMP7S2c1</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.72</v>
+        <v>1.41</v>
       </c>
       <c r="E68" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3789,643 +3789,6 @@
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>235</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>TMP7S2b4</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>234</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>TMP7S2b3</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M70" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>225</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>TMP7S2a1</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>232</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>TMP7S2b1</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>231</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>TMP7S2a7</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M73" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>230</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>TMP7S2a6</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M74" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>229</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>TMP7S2a5</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>228</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>TMP7S2a4</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>227</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>TMP7S2a3</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>1</v>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M77" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>226</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>TMP7S2a2</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M78" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>243</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>TMP7S2e1</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>233</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>TMP7S2b2</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M80" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>244</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>TMP7S2e2</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E81" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1.932</v>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4438,7 +3801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4520,7 +3883,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>148</v>
+        <v>229</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -4529,17 +3892,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
+          <t>LP1S3a2</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06</v>
+        <v>-0.119</v>
       </c>
       <c r="F2" t="n">
-        <v>0.175</v>
+        <v>0.187</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4569,7 +3932,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>164</v>
+        <v>228</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -4578,21 +3941,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
+          <t>LP1S3a1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.023</v>
+        <v>1.079</v>
       </c>
       <c r="F3" t="n">
-        <v>0.387</v>
+        <v>0.187</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -4608,7 +3971,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.96</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
         <v>2.655</v>
@@ -4618,7 +3981,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -4627,21 +3990,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+          <t>LP1S3b4</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.21</v>
+        <v>-0.655</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -4657,7 +4020,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.96</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>2.655</v>
@@ -4667,7 +4030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>234</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -4676,21 +4039,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+          <t>LP1S3b3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.243</v>
+        <v>-0.795</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -4706,7 +4069,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.592</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
         <v>2.655</v>
@@ -4716,7 +4079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -4725,21 +4088,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+          <t>LP1S3b2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.508</v>
+        <v>-0.655</v>
       </c>
       <c r="F6" t="n">
-        <v>1.468</v>
+        <v>-0.014</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -4755,7 +4118,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>0.592</v>
+        <v>2.9</v>
       </c>
       <c r="M6" t="n">
         <v>2.655</v>
@@ -4765,7 +4128,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>149</v>
+        <v>232</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -4774,21 +4137,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
+          <t>LP1S3b1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.17</v>
+        <v>-0.795</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.375</v>
+        <v>-0.014</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4804,7 +4167,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.592</v>
+        <v>2.9</v>
       </c>
       <c r="M7" t="n">
         <v>2.655</v>
@@ -4814,7 +4177,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -4823,21 +4186,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+          <t>LP1S3a4</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.45</v>
+        <v>-0.119</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.453</v>
+        <v>-2.237</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -4853,7 +4216,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M8" t="n">
         <v>2.655</v>
@@ -4863,7 +4226,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>158</v>
+        <v>230</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -4872,21 +4235,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+          <t>LP1S3a3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.575</v>
+        <v>1.079</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.024</v>
+        <v>-2.237</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -4902,7 +4265,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M9" t="n">
         <v>2.655</v>
@@ -4912,7 +4275,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -4921,21 +4284,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+          <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.45</v>
+        <v>0.06</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.175</v>
+        <v>0.175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -4951,7 +4314,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
         <v>2.655</v>
@@ -4961,7 +4324,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -4970,21 +4333,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BSS.GESSI,BM.49001:Default:1090988</t>
+          <t>LP3S3c4</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.45</v>
+        <v>0.123</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.175</v>
+        <v>-0.188</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -5000,7 +4363,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M11" t="n">
         <v>2.655</v>
@@ -5010,7 +4373,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -5019,21 +4382,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+          <t>LP3S3a1</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8</v>
+        <v>1.079</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.725</v>
+        <v>0.187</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -5049,7 +4412,7 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M12" t="n">
         <v>2.655</v>
@@ -5059,7 +4422,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -5068,21 +4431,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
+          <t>LP3S3a2</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.119</v>
       </c>
       <c r="F13" t="n">
-        <v>0.125</v>
+        <v>0.187</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -5098,7 +4461,7 @@
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M13" t="n">
         <v>2.655</v>
@@ -5108,7 +4471,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>139</v>
+        <v>238</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -5117,21 +4480,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BSS.TECE.CONCEALED CISTERN.9370224:BSS.TECE.CONCEALED CISTERN.9370224:1090923</t>
+          <t>LP3S3a3</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.705</v>
+        <v>1.079</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2</v>
+        <v>-2.237</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -5147,7 +4510,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M14" t="n">
         <v>2.655</v>
@@ -5157,7 +4520,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5166,21 +4529,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+          <t>LP3S3a4</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.28</v>
+        <v>-0.119</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.79</v>
+        <v>-2.237</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -5196,7 +4559,7 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M15" t="n">
         <v>2.655</v>
@@ -5206,7 +4569,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -5215,21 +4578,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+          <t>LP3S3b1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.037</v>
+        <v>0.75</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8</v>
+        <v>1.059</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.365</v>
+        <v>1.541</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -5245,7 +4608,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M16" t="n">
         <v>2.655</v>
@@ -5255,7 +4618,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5264,21 +4627,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+          <t>LP3S3b2</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.09</v>
+        <v>0.75</v>
       </c>
       <c r="E17" t="n">
-        <v>0.525</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.825</v>
+        <v>1.541</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -5294,7 +4657,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M17" t="n">
         <v>2.655</v>
@@ -5304,7 +4667,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -5313,21 +4676,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+          <t>LP3S3b3</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="E18" t="n">
-        <v>0.375</v>
+        <v>1.059</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9</v>
+        <v>1.259</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -5343,13 +4706,1091 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M18" t="n">
         <v>2.655</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>243</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LP3S3b4</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>244</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LP3S3c1</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.077</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>245</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LP3S3c2</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>246</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LP3S3c3</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.077</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.188</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.468</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>147</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>58</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>61</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.825</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>70</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.365</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>103</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>139</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BSS.TECE.CONCEALED CISTERN.9370224:BSS.TECE.CONCEALED CISTERN.9370224:1090923</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.705</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>143</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>144</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.725</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>145</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BSS.GESSI,BM.49001:Default:1090988</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>150</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>155</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.575</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.024</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.453</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>74</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>151</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>156</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,22 +443,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Point number/name</t>
+          <t>Point Name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Position X (m)</t>
+          <t>Position X</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Position Y (m)</t>
+          <t>Position Y</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Position Z (m)</t>
+          <t>Position Z</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Shape type</t>
+          <t>Shape Type</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -509,7 +509,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -518,17 +518,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TMP1S2b4</t>
+          <t>TMP1S2d1</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F2" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M2" t="n">
         <v>2.655</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -567,17 +567,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TMP1S2a4</t>
+          <t>TMP1S2f2</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9350000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="F3" t="n">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M3" t="n">
         <v>2.655</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -616,14 +616,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TMP1S2b1</t>
+          <t>TMP1S2f1</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.49</v>
+        <v>-1.35</v>
       </c>
       <c r="F4" t="n">
         <v>-0.775</v>
@@ -646,7 +646,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M4" t="n">
         <v>2.655</v>
@@ -656,7 +656,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -665,17 +665,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TMP1S2b2</t>
+          <t>TMP1S2e4</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M5" t="n">
         <v>2.655</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -714,14 +714,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TMP1S2b3</t>
+          <t>TMP1S2e3</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F6" t="n">
         <v>0.425</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M6" t="n">
         <v>2.655</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -763,17 +763,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TMP1S2f3</t>
+          <t>TMP1S2e2</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.35</v>
+        <v>-0.35</v>
       </c>
       <c r="F7" t="n">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M7" t="n">
         <v>2.655</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -812,14 +812,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TMP1S2c1</t>
+          <t>TMP1S2e1</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.47</v>
+        <v>-0.35</v>
       </c>
       <c r="F8" t="n">
         <v>-0.775</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M8" t="n">
         <v>2.655</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -861,17 +861,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TMP1S2c2</t>
+          <t>TMP1S2d4</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M9" t="n">
         <v>2.655</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -910,14 +910,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TMP1S2c3</t>
+          <t>TMP1S2d3</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F10" t="n">
         <v>0.425</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M10" t="n">
         <v>2.655</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -959,17 +959,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TMP1S2c4</t>
+          <t>TMP1S2d2</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F11" t="n">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M11" t="n">
         <v>2.655</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TMP1S2d1</t>
+          <t>TMP1S2c4</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M12" t="n">
         <v>2.655</v>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1057,17 +1057,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TMP1S2d2</t>
+          <t>TMP1S2c3</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M13" t="n">
         <v>2.655</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TMP1S2d3</t>
+          <t>TMP1S2c2</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F14" t="n">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M14" t="n">
         <v>2.655</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TMP1S2d4</t>
+          <t>TMP1S2c1</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F15" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M15" t="n">
         <v>2.655</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1204,17 +1204,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TMP1S2e1</t>
+          <t>TMP1S2f3</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
         <v>2.655</v>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TMP1S2e2</t>
+          <t>TMP1S2b4</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M17" t="n">
         <v>2.655</v>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TMP1S2e3</t>
+          <t>TMP1S2b2</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F18" t="n">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M18" t="n">
         <v>2.655</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TMP1S2e4</t>
+          <t>TMP1S2b1</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F19" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M19" t="n">
         <v>2.655</v>
@@ -1391,7 +1391,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TMP1S2a3</t>
+          <t>TMP1S2a4</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1410,7 +1410,7 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M20" t="n">
         <v>2.655</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TMP1S2f1</t>
+          <t>TMP1S2a3</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M21" t="n">
         <v>2.655</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M22" t="n">
         <v>2.655</v>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M23" t="n">
         <v>2.655</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1596,17 +1596,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TMP1S2f4</t>
+          <t>TMP1S2b3</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.35</v>
+        <v>0.49</v>
       </c>
       <c r="F24" t="n">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M24" t="n">
         <v>2.655</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TMP1S2f2</t>
+          <t>TMP1S2f4</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1655,7 +1655,7 @@
         <v>-1.35</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M25" t="n">
         <v>2.655</v>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1694,17 +1694,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TMP2S2a2</t>
+          <t>TMP2S2a1</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M26" t="n">
         <v>2.655</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TMP2S2b1</t>
+          <t>TMP2S2a2</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M27" t="n">
         <v>2.655</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F28" t="n">
         <v>-0.15</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M28" t="n">
         <v>2.655</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1841,14 +1841,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TMP2S2a1</t>
+          <t>TMP2S2b1</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="F29" t="n">
         <v>-0.75</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M29" t="n">
         <v>2.655</v>
@@ -1897,7 +1897,7 @@
         <v>0.6</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F30" t="n">
         <v>-0.775</v>
@@ -1946,7 +1946,7 @@
         <v>0.6</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>-0.175</v>
@@ -1995,7 +1995,7 @@
         <v>0.6</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F32" t="n">
         <v>0.425</v>
@@ -2044,7 +2044,7 @@
         <v>0.6</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F33" t="n">
         <v>1.025</v>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2086,17 +2086,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TMP4S2a4</t>
+          <t>TMP4S2a3</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0.96</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F34" t="n">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>0.592</v>
+        <v>0.6</v>
       </c>
       <c r="M34" t="n">
         <v>2.655</v>
@@ -2142,7 +2142,7 @@
         <v>0.96</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F35" t="n">
         <v>-0.175</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>0.592</v>
+        <v>0.6</v>
       </c>
       <c r="M35" t="n">
         <v>2.655</v>
@@ -2191,7 +2191,7 @@
         <v>0.96</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F36" t="n">
         <v>-0.775</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>0.592</v>
+        <v>0.6</v>
       </c>
       <c r="M36" t="n">
         <v>2.655</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2233,17 +2233,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TMP4S2a3</t>
+          <t>TMP4S2a4</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0.96</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F37" t="n">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>0.592</v>
+        <v>0.6</v>
       </c>
       <c r="M37" t="n">
         <v>2.655</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="F38" t="n">
         <v>-0.775</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M38" t="n">
         <v>2.655</v>
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="F39" t="n">
         <v>-0.775</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
         <v>2.655</v>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.45</v>
+        <v>0.03</v>
       </c>
       <c r="F40" t="n">
         <v>-0.775</v>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M40" t="n">
         <v>2.655</v>
@@ -2429,21 +2429,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TMP6S2a1</t>
+          <t>TMP5S2b1</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3</v>
+        <v>1.155</v>
       </c>
       <c r="F41" t="n">
         <v>-0.775</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="M41" t="n">
         <v>2.655</v>
@@ -2478,21 +2478,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TMP6S2a2</t>
+          <t>TMP5S2b2</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3</v>
+        <v>1.155</v>
       </c>
       <c r="F42" t="n">
         <v>-0.175</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
         <v>2.655</v>
@@ -2527,21 +2527,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TMP6S2a3</t>
+          <t>TMP5S2b3</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3</v>
+        <v>1.155</v>
       </c>
       <c r="F43" t="n">
         <v>0.425</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
         <v>2.655</v>
@@ -2576,21 +2576,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TMP6S2a4</t>
+          <t>TMP5S2b4</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3</v>
+        <v>1.155</v>
       </c>
       <c r="F44" t="n">
         <v>1.025</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="M44" t="n">
         <v>2.655</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TMP6S2b1</t>
+          <t>TMP6S2a4</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
         <v>2.655</v>
@@ -2674,14 +2674,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TMP6S2b2</t>
+          <t>TMP6S2a2</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F46" t="n">
         <v>-0.175</v>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
         <v>2.655</v>
@@ -2723,14 +2723,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TMP6S2b3</t>
+          <t>TMP6S2a3</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F47" t="n">
         <v>0.425</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
         <v>2.655</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TMP6S2b4</t>
+          <t>TMP6S2b1</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2782,7 +2782,7 @@
         <v>-0.3</v>
       </c>
       <c r="F48" t="n">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="M48" t="n">
         <v>2.655</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TMP7S2a7</t>
+          <t>TMP6S2a1</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>-0.775</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TMP7S2a1</t>
+          <t>TMP6S2b3</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.425</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M50" t="n">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TMP7S2a2</t>
+          <t>TMP6S2b4</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1.025</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -2949,17 +2949,17 @@
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2968,21 +2968,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TMP7S2a3</t>
+          <t>TMP6S2b2</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-0.175</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2998,17 +2998,17 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3017,17 +3017,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TMP7S2b1</t>
+          <t>TMP7S2a5</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E53" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3047,17 +3047,17 @@
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M53" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3066,17 +3066,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TMP7S2b2</t>
+          <t>TMP7S2e1</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.72</v>
+        <v>2.61</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3096,17 +3096,17 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M54" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3115,17 +3115,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TMP7S2b3</t>
+          <t>TMP7S2a1</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E55" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M55" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3164,17 +3164,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TMP7S2b4</t>
+          <t>TMP7S2a2</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3194,17 +3194,17 @@
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M56" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3213,17 +3213,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TMP7S2b5</t>
+          <t>TMP7S2a3</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E57" t="n">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3243,17 +3243,17 @@
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M57" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3262,17 +3262,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TMP7S2b6</t>
+          <t>TMP7S2a4</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3292,17 +3292,17 @@
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M58" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>0.9</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3341,17 +3341,17 @@
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M59" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3360,17 +3360,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TMP7S2b7</t>
+          <t>TMP7S2a7</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E60" t="n">
         <v>1.05</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3390,17 +3390,17 @@
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M60" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3409,17 +3409,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TMP7S2c2</t>
+          <t>TMP7S2e2</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.41</v>
+        <v>2.61</v>
       </c>
       <c r="E61" t="n">
         <v>1.2</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3439,17 +3439,17 @@
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M61" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3458,17 +3458,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TMP7S2d1</t>
+          <t>TMP7S2b1</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2.01</v>
+        <v>0.72</v>
       </c>
       <c r="E62" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M62" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3507,17 +3507,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TMP7S2d2</t>
+          <t>TMP7S2b3</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2.01</v>
+        <v>0.72</v>
       </c>
       <c r="E63" t="n">
-        <v>1.2</v>
+        <v>0.45</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M63" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3556,17 +3556,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TMP7S2e1</t>
+          <t>TMP7S2b4</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2.61</v>
+        <v>0.72</v>
       </c>
       <c r="E64" t="n">
         <v>0.6</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3586,17 +3586,17 @@
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M64" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3605,17 +3605,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TMP7S2e2</t>
+          <t>TMP7S2b5</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2.61</v>
+        <v>0.72</v>
       </c>
       <c r="E65" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3635,17 +3635,17 @@
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M65" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3654,17 +3654,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TMP7S2a4</t>
+          <t>TMP7S2b6</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E66" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3684,17 +3684,17 @@
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M66" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3703,17 +3703,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TMP7S2a5</t>
+          <t>TMP7S2b7</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E67" t="n">
-        <v>0.75</v>
+        <v>1.05</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3733,17 +3733,17 @@
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M67" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>0.6</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3782,13 +3782,209 @@
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M68" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>227</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TMP7S2c2</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>228</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TMP7S2d1</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>229</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TMP7S2d2</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>220</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>TMP7S2b2</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3801,7 +3997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3817,22 +4013,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Point number/name</t>
+          <t>Point Name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Position X (m)</t>
+          <t>Position X</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Position Y (m)</t>
+          <t>Position Y</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Position Z (m)</t>
+          <t>Position Z</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -3842,7 +4038,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Shape type</t>
+          <t>Shape Type</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3883,7 +4079,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -3892,17 +4088,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LP1S3a2</t>
+          <t>LP1S3a4</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.119</v>
+        <v>-0.255</v>
       </c>
       <c r="F2" t="n">
-        <v>0.187</v>
+        <v>0.137</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3922,7 +4118,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M2" t="n">
         <v>2.655</v>
@@ -3932,7 +4128,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -3941,17 +4137,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LP1S3a1</t>
+          <t>LP1S3a3</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.079</v>
+        <v>0.375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.187</v>
+        <v>0.137</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3971,7 +4167,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M3" t="n">
         <v>2.655</v>
@@ -3981,7 +4177,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -3990,17 +4186,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LP1S3b4</t>
+          <t>LP1S3a2</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.655</v>
+        <v>-0.255</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4020,7 +4216,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M4" t="n">
         <v>2.655</v>
@@ -4030,7 +4226,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -4039,17 +4235,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LP1S3b3</t>
+          <t>LP1S3a1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.795</v>
+        <v>0.375</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4069,7 +4265,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M5" t="n">
         <v>2.655</v>
@@ -4079,7 +4275,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>233</v>
+        <v>144</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -4088,17 +4284,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LP1S3b2</t>
+          <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.655</v>
+        <v>0.06</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.014</v>
+        <v>0.175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4118,7 +4314,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M6" t="n">
         <v>2.655</v>
@@ -4128,7 +4324,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -4137,21 +4333,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LP1S3b1</t>
+          <t>LP3S3a2</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.795</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.014</v>
+        <v>0.962</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4167,7 +4363,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>0.96</v>
       </c>
       <c r="M7" t="n">
         <v>2.655</v>
@@ -4177,7 +4373,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -4186,21 +4382,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LP1S3a4</t>
+          <t>LP3S3a3</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.119</v>
+        <v>-1.012</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.237</v>
+        <v>-0.188</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -4216,7 +4412,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>0.96</v>
       </c>
       <c r="M8" t="n">
         <v>2.655</v>
@@ -4226,7 +4422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -4235,21 +4431,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LP1S3a3</t>
+          <t>LP3S3a1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
-        <v>1.079</v>
+        <v>-1.012</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.237</v>
+        <v>0.962</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -4265,7 +4461,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>2.9</v>
+        <v>0.96</v>
       </c>
       <c r="M9" t="n">
         <v>2.655</v>
@@ -4275,7 +4471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>146</v>
+        <v>239</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -4284,21 +4480,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
+          <t>LP3S3a4</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.175</v>
+        <v>-0.188</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -4314,7 +4510,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>0.96</v>
       </c>
       <c r="M10" t="n">
         <v>2.655</v>
@@ -4324,7 +4520,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -4333,17 +4529,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LP3S3c4</t>
+          <t>LP3S3b1</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.123</v>
+        <v>-0.795</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.188</v>
+        <v>-0.014</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4373,7 +4569,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -4382,17 +4578,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LP3S3a1</t>
+          <t>LP3S3b2</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>1.079</v>
+        <v>-0.655</v>
       </c>
       <c r="F12" t="n">
-        <v>0.187</v>
+        <v>-0.014</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4422,7 +4618,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -4431,17 +4627,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LP3S3a2</t>
+          <t>LP3S3b3</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.119</v>
+        <v>-0.795</v>
       </c>
       <c r="F13" t="n">
-        <v>0.187</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -4471,7 +4667,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -4480,17 +4676,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LP3S3a3</t>
+          <t>LP3S3b4</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>1.079</v>
+        <v>-0.655</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.237</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -4520,7 +4716,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>239</v>
+        <v>142</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -4529,17 +4725,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LP3S3a4</t>
+          <t>BSS.GESSI.SM.49079:29046000:1090989</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.119</v>
+        <v>-0.725</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.237</v>
+        <v>-0.05</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -4569,7 +4765,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -4578,17 +4774,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LP3S3b1</t>
+          <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>1.059</v>
+        <v>-0.912</v>
       </c>
       <c r="F16" t="n">
-        <v>1.541</v>
+        <v>0.387</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -4618,7 +4814,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -4627,21 +4823,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LP3S3b2</t>
+          <t>LP4S3a2</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>0.96</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.455</v>
       </c>
       <c r="F17" t="n">
-        <v>1.541</v>
+        <v>-0.375</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -4657,7 +4853,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="n">
         <v>2.655</v>
@@ -4667,7 +4863,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -4676,21 +4872,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LP3S3b3</t>
+          <t>LP4S3a1</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.75</v>
+        <v>0.96</v>
       </c>
       <c r="E18" t="n">
-        <v>1.059</v>
+        <v>0.405</v>
       </c>
       <c r="F18" t="n">
-        <v>1.259</v>
+        <v>-0.375</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4706,7 +4902,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="M18" t="n">
         <v>2.655</v>
@@ -4716,7 +4912,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>243</v>
+        <v>145</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4725,21 +4921,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LP3S3b4</t>
+          <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.75</v>
+        <v>0.96</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="F19" t="n">
-        <v>1.259</v>
+        <v>-0.375</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4755,7 +4951,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="M19" t="n">
         <v>2.655</v>
@@ -4765,7 +4961,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4774,21 +4970,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LP3S3c1</t>
+          <t>LP5S3c1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.077</v>
+        <v>-0.42</v>
       </c>
       <c r="F20" t="n">
-        <v>0.962</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4804,7 +5000,7 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
         <v>2.655</v>
@@ -4814,7 +5010,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4823,21 +5019,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LP3S3c2</t>
+          <t>LP5S3c3</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.123</v>
+        <v>-0.42</v>
       </c>
       <c r="F21" t="n">
-        <v>0.962</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4853,7 +5049,7 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
         <v>2.655</v>
@@ -4863,7 +5059,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4872,21 +5068,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LP3S3c3</t>
+          <t>LP5S3c4</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.077</v>
+        <v>1.38</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.188</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4902,7 +5098,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
         <v>2.655</v>
@@ -4912,7 +5108,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8</v>
+        <v>260</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4921,21 +5117,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+          <t>LP5S3d1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.9370000000000001</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.243</v>
+        <v>-0.42</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8</v>
+        <v>-0.15</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4951,7 +5147,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>0.592</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
         <v>2.655</v>
@@ -4961,7 +5157,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4970,21 +5166,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+          <t>LP5S3d2</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.508</v>
+        <v>1.38</v>
       </c>
       <c r="F24" t="n">
-        <v>1.468</v>
+        <v>-0.15</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -5000,7 +5196,7 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0.592</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
         <v>2.655</v>
@@ -5010,7 +5206,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5019,21 +5215,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
+          <t>LP5S3c2</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.17</v>
+        <v>1.38</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.375</v>
+        <v>1.4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -5049,7 +5245,7 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.592</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
         <v>2.655</v>
@@ -5059,7 +5255,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5068,17 +5264,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+          <t>LP5S3d3</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.375</v>
+        <v>-0.42</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9</v>
+        <v>-0.75</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -5098,7 +5294,7 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
         <v>2.655</v>
@@ -5108,7 +5304,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5117,17 +5313,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+          <t>LP5S3b2</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.09</v>
+        <v>0.183</v>
       </c>
       <c r="E27" t="n">
-        <v>0.525</v>
+        <v>0.21</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.825</v>
+        <v>-0.402</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -5147,7 +5343,7 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
         <v>2.655</v>
@@ -5157,7 +5353,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>70</v>
+        <v>251</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5166,17 +5362,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+          <t>LP5S3b1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.037</v>
+        <v>0.183</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8</v>
+        <v>-0.15</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.365</v>
+        <v>-0.402</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -5196,7 +5392,7 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
         <v>2.655</v>
@@ -5206,7 +5402,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5215,17 +5411,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+          <t>LP5S3a5</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.435</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.28</v>
+        <v>0.025</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.79</v>
+        <v>-0.22</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -5245,7 +5441,7 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
         <v>2.655</v>
@@ -5255,7 +5451,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>139</v>
+        <v>246</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5264,17 +5460,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BSS.TECE.CONCEALED CISTERN.9370224:BSS.TECE.CONCEALED CISTERN.9370224:1090923</t>
+          <t>LP5S3a1</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0.08799999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.705</v>
+        <v>-0.225</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.2</v>
+        <v>0.026</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5294,7 +5490,7 @@
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
         <v>2.655</v>
@@ -5304,7 +5500,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>143</v>
+        <v>247</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -5313,17 +5509,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
+          <t>LP5S3a2</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="F31" t="n">
-        <v>0.125</v>
+        <v>0.026</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -5343,7 +5539,7 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
         <v>2.655</v>
@@ -5353,7 +5549,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -5362,17 +5558,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+          <t>LP5S3a3</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.22</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8</v>
+        <v>-0.225</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.725</v>
+        <v>-0.466</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -5392,7 +5588,7 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
         <v>2.655</v>
@@ -5402,7 +5598,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>145</v>
+        <v>249</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -5411,17 +5607,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BSS.GESSI,BM.49001:Default:1090988</t>
+          <t>LP5S3a4</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.06</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.45</v>
+        <v>0.275</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.175</v>
+        <v>-0.466</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5441,7 +5637,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M33" t="n">
         <v>2.655</v>
@@ -5451,7 +5647,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>150</v>
+        <v>253</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -5460,17 +5656,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+          <t>LP5S3b3</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.108</v>
+        <v>0.183</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.175</v>
+        <v>-0.83</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5490,7 +5686,7 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
         <v>2.655</v>
@@ -5500,7 +5696,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -5509,17 +5705,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+          <t>LP5S3d4</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.575</v>
+        <v>1.38</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.024</v>
+        <v>-0.75</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5539,7 +5735,7 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
         <v>2.655</v>
@@ -5549,7 +5745,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -5558,17 +5754,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+          <t>LP5S3b5</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.295</v>
+        <v>0.183</v>
       </c>
       <c r="E36" t="n">
-        <v>0.45</v>
+        <v>0.03</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.453</v>
+        <v>-0.616</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5588,7 +5784,7 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
         <v>2.655</v>
@@ -5598,7 +5794,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -5607,21 +5803,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
+          <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.645</v>
+        <v>0.108</v>
       </c>
       <c r="E37" t="n">
-        <v>1.112</v>
+        <v>0.03</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-0.175</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5637,17 +5833,17 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M37" t="n">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5656,21 +5852,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
+          <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.01</v>
+        <v>0.208</v>
       </c>
       <c r="E38" t="n">
-        <v>1.535</v>
+        <v>-0.095</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-1.024</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5686,17 +5882,17 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M38" t="n">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5705,21 +5901,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
+          <t>LP5S3b4</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.01</v>
+        <v>0.183</v>
       </c>
       <c r="E39" t="n">
-        <v>1.535</v>
+        <v>0.21</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5735,17 +5931,17 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>156</v>
+        <v>264</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5754,17 +5950,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
+          <t>LP7S3a1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.645</v>
+        <v>0.57</v>
       </c>
       <c r="E40" t="n">
-        <v>1.075</v>
+        <v>1.15</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5784,13 +5980,454 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M40" t="n">
-        <v>1.932</v>
+        <v>1.8</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>266</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LP7S3a3</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>277</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LP7S3b2</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>267</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LP7S3a4</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>276</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LP7S3b1</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>270</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LP7S3b3</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>271</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LP7S3b4</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>6</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>273</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LP7S3a2</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>6</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>150</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>6</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>155</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fitting</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform-linux/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.03</v>
       </c>
       <c r="F2" t="n">
         <v>-0.775</v>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.35</v>
       </c>
       <c r="F3" t="n">
         <v>-0.175</v>
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1.35</v>
       </c>
       <c r="F4" t="n">
         <v>-0.775</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.35</v>
       </c>
       <c r="F5" t="n">
         <v>1.025</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.35</v>
       </c>
       <c r="F6" t="n">
         <v>0.425</v>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.35</v>
       </c>
       <c r="F7" t="n">
         <v>-0.175</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.35</v>
       </c>
       <c r="F8" t="n">
         <v>-0.775</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.03</v>
       </c>
       <c r="F9" t="n">
         <v>1.025</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.03</v>
       </c>
       <c r="F10" t="n">
         <v>0.425</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.03</v>
       </c>
       <c r="F11" t="n">
         <v>-0.175</v>
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E12" t="n">
         <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.47</v>
       </c>
       <c r="F12" t="n">
         <v>1.025</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E13" t="n">
         <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.47</v>
       </c>
       <c r="F13" t="n">
         <v>0.425</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E14" t="n">
         <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.47</v>
       </c>
       <c r="F14" t="n">
         <v>-0.175</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E15" t="n">
         <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.47</v>
       </c>
       <c r="F15" t="n">
         <v>-0.775</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E16" t="n">
         <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-1.35</v>
       </c>
       <c r="F16" t="n">
         <v>0.425</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E17" t="n">
         <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.49</v>
       </c>
       <c r="F17" t="n">
         <v>1.025</v>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="D18" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E18" t="n">
         <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.49</v>
       </c>
       <c r="F18" t="n">
         <v>-0.175</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D19" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E19" t="n">
         <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.49</v>
       </c>
       <c r="F19" t="n">
         <v>-0.775</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="D20" t="n">
+        <v>-0.9350000000000001</v>
+      </c>
+      <c r="E20" t="n">
         <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.9350000000000001</v>
       </c>
       <c r="F20" t="n">
         <v>1.025</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>-0.9350000000000001</v>
+      </c>
+      <c r="E21" t="n">
         <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.9350000000000001</v>
       </c>
       <c r="F21" t="n">
         <v>0.425</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>-0.9350000000000001</v>
+      </c>
+      <c r="E22" t="n">
         <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.9350000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>-0.175</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="D23" t="n">
+        <v>-0.9350000000000001</v>
+      </c>
+      <c r="E23" t="n">
         <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.9350000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>-0.775</v>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="D24" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E24" t="n">
         <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.49</v>
       </c>
       <c r="F24" t="n">
         <v>0.425</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="D25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E25" t="n">
         <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-1.35</v>
       </c>
       <c r="F25" t="n">
         <v>1.025</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="D26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E26" t="n">
         <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.8</v>
       </c>
       <c r="F26" t="n">
         <v>-0.75</v>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="D27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E27" t="n">
         <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-0.8</v>
       </c>
       <c r="F27" t="n">
         <v>-0.15</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="D28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E28" t="n">
         <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0.2</v>
       </c>
       <c r="F28" t="n">
         <v>-0.15</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E29" t="n">
         <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.2</v>
       </c>
       <c r="F29" t="n">
         <v>-0.75</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="D30" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0.9350000000000001</v>
       </c>
       <c r="F30" t="n">
         <v>-0.775</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="D31" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E31" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0.9350000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>-0.175</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="D32" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E32" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-0.9350000000000001</v>
       </c>
       <c r="F32" t="n">
         <v>0.425</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D33" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E33" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-0.9350000000000001</v>
       </c>
       <c r="F33" t="n">
         <v>1.025</v>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E34" t="n">
         <v>0.96</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.3</v>
       </c>
       <c r="F34" t="n">
         <v>0.425</v>
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.96</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.3</v>
       </c>
       <c r="F35" t="n">
         <v>-0.175</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="D36" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.96</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.3</v>
       </c>
       <c r="F36" t="n">
         <v>-0.775</v>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="D37" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.96</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.3</v>
       </c>
       <c r="F37" t="n">
         <v>1.025</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="D38" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="E38" t="n">
         <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.93</v>
       </c>
       <c r="F38" t="n">
         <v>-0.775</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="D39" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="E39" t="n">
         <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.48</v>
       </c>
       <c r="F39" t="n">
         <v>-0.775</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="D40" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E40" t="n">
         <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.03</v>
       </c>
       <c r="F40" t="n">
         <v>-0.775</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D41" t="n">
+        <v>-1.155</v>
+      </c>
+      <c r="E41" t="n">
         <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1.155</v>
       </c>
       <c r="F41" t="n">
         <v>-0.775</v>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="D42" t="n">
+        <v>-1.155</v>
+      </c>
+      <c r="E42" t="n">
         <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1.155</v>
       </c>
       <c r="F42" t="n">
         <v>-0.175</v>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D43" t="n">
+        <v>-1.155</v>
+      </c>
+      <c r="E43" t="n">
         <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1.155</v>
       </c>
       <c r="F43" t="n">
         <v>0.425</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="D44" t="n">
+        <v>-1.155</v>
+      </c>
+      <c r="E44" t="n">
         <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1.155</v>
       </c>
       <c r="F44" t="n">
         <v>1.025</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="D45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E45" t="n">
         <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.3</v>
       </c>
       <c r="F45" t="n">
         <v>1.025</v>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E46" t="n">
         <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.3</v>
       </c>
       <c r="F46" t="n">
         <v>-0.175</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E47" t="n">
         <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.3</v>
       </c>
       <c r="F47" t="n">
         <v>0.425</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E48" t="n">
         <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-0.3</v>
       </c>
       <c r="F48" t="n">
         <v>-0.775</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E49" t="n">
         <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.3</v>
       </c>
       <c r="F49" t="n">
         <v>-0.775</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E50" t="n">
         <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-0.3</v>
       </c>
       <c r="F50" t="n">
         <v>0.425</v>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="D51" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E51" t="n">
         <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-0.3</v>
       </c>
       <c r="F51" t="n">
         <v>1.025</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="D52" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E52" t="n">
         <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-0.3</v>
       </c>
       <c r="F52" t="n">
         <v>-0.175</v>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.12</v>
+        <v>-1.26</v>
       </c>
       <c r="E53" t="n">
-        <v>0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.61</v>
+        <v>1.23</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.12</v>
+        <v>-1.26</v>
       </c>
       <c r="E55" t="n">
-        <v>0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3168,13 +3168,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.12</v>
+        <v>-1.26</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.12</v>
+        <v>-1.26</v>
       </c>
       <c r="E57" t="n">
-        <v>0.45</v>
+        <v>-0.45</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3266,13 +3266,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.12</v>
+        <v>-1.26</v>
       </c>
       <c r="E58" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.12</v>
+        <v>-1.26</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.12</v>
+        <v>-1.26</v>
       </c>
       <c r="E60" t="n">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3413,13 +3413,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2.61</v>
+        <v>1.23</v>
       </c>
       <c r="E61" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3462,13 +3462,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E62" t="n">
-        <v>0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E63" t="n">
-        <v>0.45</v>
+        <v>-0.45</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E65" t="n">
-        <v>0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3707,13 +3707,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E67" t="n">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.41</v>
+        <v>0.03</v>
       </c>
       <c r="E68" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3805,13 +3805,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.41</v>
+        <v>0.03</v>
       </c>
       <c r="E69" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2.01</v>
+        <v>0.63</v>
       </c>
       <c r="E70" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.01</v>
+        <v>0.63</v>
       </c>
       <c r="E71" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E72" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.255</v>
       </c>
       <c r="F2" t="n">
         <v>0.137</v>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.375</v>
       </c>
       <c r="F3" t="n">
         <v>0.137</v>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.255</v>
       </c>
       <c r="F4" t="n">
         <v>0.213</v>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.375</v>
       </c>
       <c r="F5" t="n">
         <v>0.213</v>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.06</v>
       </c>
       <c r="F6" t="n">
         <v>0.175</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.8120000000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0.962</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-1.012</v>
       </c>
       <c r="F8" t="n">
         <v>-0.188</v>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-1.012</v>
       </c>
       <c r="F9" t="n">
         <v>0.962</v>
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.8120000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>-0.188</v>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.795</v>
       </c>
       <c r="F11" t="n">
         <v>-0.014</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.655</v>
       </c>
       <c r="F12" t="n">
         <v>-0.014</v>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.795</v>
       </c>
       <c r="F13" t="n">
         <v>-0.08599999999999999</v>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.655</v>
       </c>
       <c r="F14" t="n">
         <v>-0.08599999999999999</v>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E15" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.725</v>
       </c>
       <c r="F15" t="n">
         <v>-0.05</v>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0.912</v>
       </c>
       <c r="F16" t="n">
         <v>0.387</v>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>-0.455</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.96</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.455</v>
       </c>
       <c r="F17" t="n">
         <v>-0.375</v>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="D18" t="n">
+        <v>-0.405</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.96</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.405</v>
       </c>
       <c r="F18" t="n">
         <v>-0.375</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="D19" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.96</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.43</v>
       </c>
       <c r="F19" t="n">
         <v>-0.375</v>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="D20" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E20" t="n">
         <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.42</v>
       </c>
       <c r="F20" t="n">
         <v>1.4</v>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E21" t="n">
         <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.42</v>
       </c>
       <c r="F21" t="n">
         <v>1.4</v>
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="E22" t="n">
         <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.38</v>
       </c>
       <c r="F22" t="n">
         <v>1.4</v>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="D23" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E23" t="n">
         <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-0.42</v>
       </c>
       <c r="F23" t="n">
         <v>-0.15</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="D24" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="E24" t="n">
         <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.38</v>
       </c>
       <c r="F24" t="n">
         <v>-0.15</v>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="D25" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="E25" t="n">
         <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.38</v>
       </c>
       <c r="F25" t="n">
         <v>1.4</v>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D26" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E26" t="n">
         <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.42</v>
       </c>
       <c r="F26" t="n">
         <v>-0.75</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D27" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.183</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.21</v>
       </c>
       <c r="F27" t="n">
         <v>-0.402</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="D28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E28" t="n">
         <v>0.183</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0.15</v>
       </c>
       <c r="F28" t="n">
         <v>-0.402</v>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D29" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="E29" t="n">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.025</v>
       </c>
       <c r="F29" t="n">
         <v>-0.22</v>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="D30" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0.225</v>
       </c>
       <c r="F30" t="n">
         <v>0.026</v>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="D31" t="n">
+        <v>-0.275</v>
+      </c>
+      <c r="E31" t="n">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.275</v>
       </c>
       <c r="F31" t="n">
         <v>0.026</v>
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="D32" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E32" t="n">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-0.225</v>
       </c>
       <c r="F32" t="n">
         <v>-0.466</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="D33" t="n">
+        <v>-0.275</v>
+      </c>
+      <c r="E33" t="n">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.275</v>
       </c>
       <c r="F33" t="n">
         <v>-0.466</v>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E34" t="n">
         <v>0.183</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.15</v>
       </c>
       <c r="F34" t="n">
         <v>-0.83</v>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="E35" t="n">
         <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.38</v>
       </c>
       <c r="F35" t="n">
         <v>-0.75</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="D36" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.183</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.03</v>
       </c>
       <c r="F36" t="n">
         <v>-0.616</v>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="D37" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.108</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.03</v>
       </c>
       <c r="F37" t="n">
         <v>-0.175</v>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="D38" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.208</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-0.095</v>
       </c>
       <c r="F38" t="n">
         <v>-1.024</v>
@@ -5905,10 +5905,10 @@
         </is>
       </c>
       <c r="D39" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E39" t="n">
         <v>0.183</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.21</v>
       </c>
       <c r="F39" t="n">
         <v>-0.83</v>
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.57</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>1.15</v>
+        <v>0.25</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6003,13 +6003,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.57</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.06</v>
+        <v>-0.32</v>
       </c>
       <c r="E42" t="n">
-        <v>1.585</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6101,13 +6101,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -6150,13 +6150,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.96</v>
+        <v>-0.42</v>
       </c>
       <c r="E44" t="n">
-        <v>1.585</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -6199,13 +6199,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.96</v>
+        <v>-0.42</v>
       </c>
       <c r="E45" t="n">
-        <v>1.485</v>
+        <v>0.585</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -6248,13 +6248,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.06</v>
+        <v>-0.32</v>
       </c>
       <c r="E46" t="n">
-        <v>1.485</v>
+        <v>0.585</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -6297,13 +6297,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="E47" t="n">
-        <v>1.15</v>
+        <v>0.25</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6346,13 +6346,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1.01</v>
+        <v>-0.37</v>
       </c>
       <c r="E48" t="n">
-        <v>1.535</v>
+        <v>0.635</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6395,13 +6395,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.645</v>
+        <v>-0.735</v>
       </c>
       <c r="E49" t="n">
-        <v>1.075</v>
+        <v>0.175</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
